--- a/data/macro/Japan CPI YoY.xlsx
+++ b/data/macro/Japan CPI YoY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242F6F8D-E739-4921-B7BC-44275D81279F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEF0BE5-0D32-1C40-BD31-B60FA465F1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" xr2:uid="{A0358DA5-9C11-4628-B2D7-24F5FD1145D7}"/>
+    <workbookView xWindow="5240" yWindow="1580" windowWidth="28800" windowHeight="17000" xr2:uid="{A0358DA5-9C11-4628-B2D7-24F5FD1145D7}"/>
   </bookViews>
   <sheets>
     <sheet name="JPCPI YoY" sheetId="1" r:id="rId1"/>
@@ -67,9 +67,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -114,7 +114,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -124,10 +124,10 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -136,21 +136,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -166,9 +157,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -206,7 +197,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -312,7 +303,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -454,7 +445,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -463,15 +454,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546E751-EA49-4715-8697-66309DE54846}">
   <dimension ref="A1:G660"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -490,8 +481,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+    <row r="2" spans="1:7">
+      <c r="A2" s="4">
         <v>25934</v>
       </c>
       <c r="B2" s="4">
@@ -505,8 +496,8 @@
       </c>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+    <row r="3" spans="1:7">
+      <c r="A3" s="4">
         <v>25965</v>
       </c>
       <c r="B3" s="4">
@@ -523,8 +514,8 @@
       </c>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+    <row r="4" spans="1:7">
+      <c r="A4" s="4">
         <v>25993</v>
       </c>
       <c r="B4" s="4">
@@ -541,8 +532,8 @@
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+    <row r="5" spans="1:7">
+      <c r="A5" s="4">
         <v>26024</v>
       </c>
       <c r="B5" s="4">
@@ -559,8 +550,8 @@
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+    <row r="6" spans="1:7">
+      <c r="A6" s="4">
         <v>26054</v>
       </c>
       <c r="B6" s="4">
@@ -577,8 +568,8 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+    <row r="7" spans="1:7">
+      <c r="A7" s="4">
         <v>26085</v>
       </c>
       <c r="B7" s="4">
@@ -595,8 +586,8 @@
       </c>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+    <row r="8" spans="1:7">
+      <c r="A8" s="4">
         <v>26115</v>
       </c>
       <c r="B8" s="4">
@@ -613,8 +604,8 @@
       </c>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+    <row r="9" spans="1:7">
+      <c r="A9" s="4">
         <v>26146</v>
       </c>
       <c r="B9" s="4">
@@ -631,8 +622,8 @@
       </c>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+    <row r="10" spans="1:7">
+      <c r="A10" s="4">
         <v>26177</v>
       </c>
       <c r="B10" s="4">
@@ -649,8 +640,8 @@
       </c>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+    <row r="11" spans="1:7">
+      <c r="A11" s="4">
         <v>26207</v>
       </c>
       <c r="B11" s="4">
@@ -667,8 +658,8 @@
       </c>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+    <row r="12" spans="1:7">
+      <c r="A12" s="4">
         <v>26238</v>
       </c>
       <c r="B12" s="4">
@@ -685,8 +676,8 @@
       </c>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+    <row r="13" spans="1:7">
+      <c r="A13" s="4">
         <v>26268</v>
       </c>
       <c r="B13" s="4">
@@ -703,8 +694,8 @@
       </c>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
+    <row r="14" spans="1:7">
+      <c r="A14" s="4">
         <v>26299</v>
       </c>
       <c r="B14" s="4">
@@ -720,8 +711,8 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+    <row r="15" spans="1:7">
+      <c r="A15" s="4">
         <v>26330</v>
       </c>
       <c r="B15" s="4">
@@ -737,8 +728,8 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
+    <row r="16" spans="1:7">
+      <c r="A16" s="4">
         <v>26359</v>
       </c>
       <c r="B16" s="4">
@@ -754,8 +745,8 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
+    <row r="17" spans="1:6">
+      <c r="A17" s="4">
         <v>26390</v>
       </c>
       <c r="B17" s="4">
@@ -771,8 +762,8 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
+    <row r="18" spans="1:6">
+      <c r="A18" s="4">
         <v>26420</v>
       </c>
       <c r="B18" s="4">
@@ -788,8 +779,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
+    <row r="19" spans="1:6">
+      <c r="A19" s="4">
         <v>26451</v>
       </c>
       <c r="B19" s="4">
@@ -805,8 +796,8 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
+    <row r="20" spans="1:6">
+      <c r="A20" s="4">
         <v>26481</v>
       </c>
       <c r="B20" s="4">
@@ -822,8 +813,8 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+    <row r="21" spans="1:6">
+      <c r="A21" s="4">
         <v>26512</v>
       </c>
       <c r="B21" s="4">
@@ -839,8 +830,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+    <row r="22" spans="1:6">
+      <c r="A22" s="4">
         <v>26543</v>
       </c>
       <c r="B22" s="4">
@@ -856,8 +847,8 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
+    <row r="23" spans="1:6">
+      <c r="A23" s="4">
         <v>26573</v>
       </c>
       <c r="B23" s="4">
@@ -873,8 +864,8 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="9">
+    <row r="24" spans="1:6">
+      <c r="A24" s="4">
         <v>26604</v>
       </c>
       <c r="B24" s="4">
@@ -890,8 +881,8 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
+    <row r="25" spans="1:6">
+      <c r="A25" s="4">
         <v>26634</v>
       </c>
       <c r="B25" s="4">
@@ -907,8 +898,8 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+    <row r="26" spans="1:6">
+      <c r="A26" s="4">
         <v>26665</v>
       </c>
       <c r="B26" s="4">
@@ -924,8 +915,8 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+    <row r="27" spans="1:6">
+      <c r="A27" s="4">
         <v>26696</v>
       </c>
       <c r="B27" s="4">
@@ -941,8 +932,8 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
+    <row r="28" spans="1:6">
+      <c r="A28" s="4">
         <v>26724</v>
       </c>
       <c r="B28" s="4">
@@ -958,8 +949,8 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
+    <row r="29" spans="1:6">
+      <c r="A29" s="4">
         <v>26755</v>
       </c>
       <c r="B29" s="4">
@@ -975,8 +966,8 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
+    <row r="30" spans="1:6">
+      <c r="A30" s="4">
         <v>26785</v>
       </c>
       <c r="B30" s="4">
@@ -992,8 +983,8 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
+    <row r="31" spans="1:6">
+      <c r="A31" s="4">
         <v>26816</v>
       </c>
       <c r="B31" s="4">
@@ -1009,8 +1000,8 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
+    <row r="32" spans="1:6">
+      <c r="A32" s="4">
         <v>26846</v>
       </c>
       <c r="B32" s="4">
@@ -1026,8 +1017,8 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
+    <row r="33" spans="1:6">
+      <c r="A33" s="4">
         <v>26877</v>
       </c>
       <c r="B33" s="4">
@@ -1043,8 +1034,8 @@
         <v>0.11700000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
+    <row r="34" spans="1:6">
+      <c r="A34" s="4">
         <v>26908</v>
       </c>
       <c r="B34" s="4">
@@ -1060,8 +1051,8 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
+    <row r="35" spans="1:6">
+      <c r="A35" s="4">
         <v>26938</v>
       </c>
       <c r="B35" s="4">
@@ -1077,8 +1068,8 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="9">
+    <row r="36" spans="1:6">
+      <c r="A36" s="4">
         <v>26969</v>
       </c>
       <c r="B36" s="4">
@@ -1094,8 +1085,8 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="9">
+    <row r="37" spans="1:6">
+      <c r="A37" s="4">
         <v>26999</v>
       </c>
       <c r="B37" s="4">
@@ -1111,8 +1102,8 @@
         <v>0.152</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="9">
+    <row r="38" spans="1:6">
+      <c r="A38" s="4">
         <v>27030</v>
       </c>
       <c r="B38" s="4">
@@ -1128,8 +1119,8 @@
         <v>0.183</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="9">
+    <row r="39" spans="1:6">
+      <c r="A39" s="4">
         <v>27061</v>
       </c>
       <c r="B39" s="4">
@@ -1145,8 +1136,8 @@
         <v>0.219</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="9">
+    <row r="40" spans="1:6">
+      <c r="A40" s="4">
         <v>27089</v>
       </c>
       <c r="B40" s="4">
@@ -1162,8 +1153,8 @@
         <v>0.249</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+    <row r="41" spans="1:6">
+      <c r="A41" s="4">
         <v>27120</v>
       </c>
       <c r="B41" s="4">
@@ -1179,8 +1170,8 @@
         <v>0.22800000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="9">
+    <row r="42" spans="1:6">
+      <c r="A42" s="4">
         <v>27150</v>
       </c>
       <c r="B42" s="4">
@@ -1196,8 +1187,8 @@
         <v>0.23699999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="9">
+    <row r="43" spans="1:6">
+      <c r="A43" s="4">
         <v>27181</v>
       </c>
       <c r="B43" s="4">
@@ -1213,8 +1204,8 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="9">
+    <row r="44" spans="1:6">
+      <c r="A44" s="4">
         <v>27211</v>
       </c>
       <c r="B44" s="4">
@@ -1230,8 +1221,8 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
+    <row r="45" spans="1:6">
+      <c r="A45" s="4">
         <v>27242</v>
       </c>
       <c r="B45" s="4">
@@ -1247,8 +1238,8 @@
         <v>0.23799999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="9">
+    <row r="46" spans="1:6">
+      <c r="A46" s="4">
         <v>27273</v>
       </c>
       <c r="B46" s="4">
@@ -1264,8 +1255,8 @@
         <v>0.23899999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="9">
+    <row r="47" spans="1:6">
+      <c r="A47" s="4">
         <v>27303</v>
       </c>
       <c r="B47" s="4">
@@ -1281,8 +1272,8 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
+    <row r="48" spans="1:6">
+      <c r="A48" s="4">
         <v>27334</v>
       </c>
       <c r="B48" s="4">
@@ -1298,8 +1289,8 @@
         <v>0.248</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="9">
+    <row r="49" spans="1:6">
+      <c r="A49" s="4">
         <v>27364</v>
       </c>
       <c r="B49" s="4">
@@ -1315,8 +1306,8 @@
         <v>0.245</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="9">
+    <row r="50" spans="1:6">
+      <c r="A50" s="4">
         <v>27395</v>
       </c>
       <c r="B50" s="4">
@@ -1332,8 +1323,8 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="9">
+    <row r="51" spans="1:6">
+      <c r="A51" s="4">
         <v>27426</v>
       </c>
       <c r="B51" s="4">
@@ -1349,8 +1340,8 @@
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="9">
+    <row r="52" spans="1:6">
+      <c r="A52" s="4">
         <v>27454</v>
       </c>
       <c r="B52" s="4">
@@ -1366,8 +1357,8 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="9">
+    <row r="53" spans="1:6">
+      <c r="A53" s="4">
         <v>27485</v>
       </c>
       <c r="B53" s="4">
@@ -1383,8 +1374,8 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="9">
+    <row r="54" spans="1:6">
+      <c r="A54" s="4">
         <v>27515</v>
       </c>
       <c r="B54" s="4">
@@ -1400,8 +1391,8 @@
         <v>0.13400000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="9">
+    <row r="55" spans="1:6">
+      <c r="A55" s="4">
         <v>27546</v>
       </c>
       <c r="B55" s="4">
@@ -1417,8 +1408,8 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="9">
+    <row r="56" spans="1:6">
+      <c r="A56" s="4">
         <v>27576</v>
       </c>
       <c r="B56" s="4">
@@ -1434,8 +1425,8 @@
         <v>0.13400000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="9">
+    <row r="57" spans="1:6">
+      <c r="A57" s="4">
         <v>27607</v>
       </c>
       <c r="B57" s="4">
@@ -1451,8 +1442,8 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="9">
+    <row r="58" spans="1:6">
+      <c r="A58" s="4">
         <v>27638</v>
       </c>
       <c r="B58" s="4">
@@ -1468,8 +1459,8 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="9">
+    <row r="59" spans="1:6">
+      <c r="A59" s="4">
         <v>27668</v>
       </c>
       <c r="B59" s="4">
@@ -1485,8 +1476,8 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="9">
+    <row r="60" spans="1:6">
+      <c r="A60" s="4">
         <v>27699</v>
       </c>
       <c r="B60" s="4">
@@ -1502,8 +1493,8 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="9">
+    <row r="61" spans="1:6">
+      <c r="A61" s="4">
         <v>27729</v>
       </c>
       <c r="B61" s="4">
@@ -1519,8 +1510,8 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="9">
+    <row r="62" spans="1:6">
+      <c r="A62" s="4">
         <v>27760</v>
       </c>
       <c r="B62" s="4">
@@ -1536,8 +1527,8 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="9">
+    <row r="63" spans="1:6">
+      <c r="A63" s="4">
         <v>27791</v>
       </c>
       <c r="B63" s="4">
@@ -1553,8 +1544,8 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="9">
+    <row r="64" spans="1:6">
+      <c r="A64" s="4">
         <v>27820</v>
       </c>
       <c r="B64" s="4">
@@ -1570,8 +1561,8 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="9">
+    <row r="65" spans="1:6">
+      <c r="A65" s="4">
         <v>27851</v>
       </c>
       <c r="B65" s="4">
@@ -1587,8 +1578,8 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="9">
+    <row r="66" spans="1:6">
+      <c r="A66" s="4">
         <v>27881</v>
       </c>
       <c r="B66" s="4">
@@ -1604,8 +1595,8 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="9">
+    <row r="67" spans="1:6">
+      <c r="A67" s="4">
         <v>27912</v>
       </c>
       <c r="B67" s="4">
@@ -1621,8 +1612,8 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="9">
+    <row r="68" spans="1:6">
+      <c r="A68" s="4">
         <v>27942</v>
       </c>
       <c r="B68" s="4">
@@ -1638,8 +1629,8 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="9">
+    <row r="69" spans="1:6">
+      <c r="A69" s="4">
         <v>27973</v>
       </c>
       <c r="B69" s="4">
@@ -1655,8 +1646,8 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="9">
+    <row r="70" spans="1:6">
+      <c r="A70" s="4">
         <v>28004</v>
       </c>
       <c r="B70" s="4">
@@ -1672,8 +1663,8 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="9">
+    <row r="71" spans="1:6">
+      <c r="A71" s="4">
         <v>28034</v>
       </c>
       <c r="B71" s="4">
@@ -1689,8 +1680,8 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="9">
+    <row r="72" spans="1:6">
+      <c r="A72" s="4">
         <v>28065</v>
       </c>
       <c r="B72" s="4">
@@ -1706,8 +1697,8 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="9">
+    <row r="73" spans="1:6">
+      <c r="A73" s="4">
         <v>28095</v>
       </c>
       <c r="B73" s="4">
@@ -1723,8 +1714,8 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="9">
+    <row r="74" spans="1:6">
+      <c r="A74" s="4">
         <v>28126</v>
       </c>
       <c r="B74" s="4">
@@ -1740,8 +1731,8 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="9">
+    <row r="75" spans="1:6">
+      <c r="A75" s="4">
         <v>28157</v>
       </c>
       <c r="B75" s="4">
@@ -1757,8 +1748,8 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="9">
+    <row r="76" spans="1:6">
+      <c r="A76" s="4">
         <v>28185</v>
       </c>
       <c r="B76" s="4">
@@ -1774,8 +1765,8 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="9">
+    <row r="77" spans="1:6">
+      <c r="A77" s="4">
         <v>28216</v>
       </c>
       <c r="B77" s="4">
@@ -1791,8 +1782,8 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="9">
+    <row r="78" spans="1:6">
+      <c r="A78" s="4">
         <v>28246</v>
       </c>
       <c r="B78" s="4">
@@ -1808,8 +1799,8 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="9">
+    <row r="79" spans="1:6">
+      <c r="A79" s="4">
         <v>28277</v>
       </c>
       <c r="B79" s="4">
@@ -1825,8 +1816,8 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="9">
+    <row r="80" spans="1:6">
+      <c r="A80" s="4">
         <v>28307</v>
       </c>
       <c r="B80" s="4">
@@ -1842,8 +1833,8 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="9">
+    <row r="81" spans="1:6">
+      <c r="A81" s="4">
         <v>28338</v>
       </c>
       <c r="B81" s="4">
@@ -1859,8 +1850,8 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="9">
+    <row r="82" spans="1:6">
+      <c r="A82" s="4">
         <v>28369</v>
       </c>
       <c r="B82" s="4">
@@ -1876,8 +1867,8 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="9">
+    <row r="83" spans="1:6">
+      <c r="A83" s="4">
         <v>28399</v>
       </c>
       <c r="B83" s="4">
@@ -1893,8 +1884,8 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="9">
+    <row r="84" spans="1:6">
+      <c r="A84" s="4">
         <v>28430</v>
       </c>
       <c r="B84" s="4">
@@ -1910,8 +1901,8 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="9">
+    <row r="85" spans="1:6">
+      <c r="A85" s="4">
         <v>28460</v>
       </c>
       <c r="B85" s="4">
@@ -1927,8 +1918,8 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="9">
+    <row r="86" spans="1:6">
+      <c r="A86" s="4">
         <v>28491</v>
       </c>
       <c r="B86" s="4">
@@ -1944,8 +1935,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="9">
+    <row r="87" spans="1:6">
+      <c r="A87" s="4">
         <v>28522</v>
       </c>
       <c r="B87" s="4">
@@ -1961,8 +1952,8 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="9">
+    <row r="88" spans="1:6">
+      <c r="A88" s="4">
         <v>28550</v>
       </c>
       <c r="B88" s="4">
@@ -1978,8 +1969,8 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="9">
+    <row r="89" spans="1:6">
+      <c r="A89" s="4">
         <v>28581</v>
       </c>
       <c r="B89" s="4">
@@ -1995,8 +1986,8 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="9">
+    <row r="90" spans="1:6">
+      <c r="A90" s="4">
         <v>28611</v>
       </c>
       <c r="B90" s="4">
@@ -2012,8 +2003,8 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="9">
+    <row r="91" spans="1:6">
+      <c r="A91" s="4">
         <v>28642</v>
       </c>
       <c r="B91" s="4">
@@ -2029,8 +2020,8 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="9">
+    <row r="92" spans="1:6">
+      <c r="A92" s="4">
         <v>28672</v>
       </c>
       <c r="B92" s="4">
@@ -2046,8 +2037,8 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="9">
+    <row r="93" spans="1:6">
+      <c r="A93" s="4">
         <v>28703</v>
       </c>
       <c r="B93" s="4">
@@ -2063,8 +2054,8 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="9">
+    <row r="94" spans="1:6">
+      <c r="A94" s="4">
         <v>28734</v>
       </c>
       <c r="B94" s="4">
@@ -2080,8 +2071,8 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="9">
+    <row r="95" spans="1:6">
+      <c r="A95" s="4">
         <v>28764</v>
       </c>
       <c r="B95" s="4">
@@ -2097,8 +2088,8 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="9">
+    <row r="96" spans="1:6">
+      <c r="A96" s="4">
         <v>28795</v>
       </c>
       <c r="B96" s="4">
@@ -2114,8 +2105,8 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="9">
+    <row r="97" spans="1:6">
+      <c r="A97" s="4">
         <v>28825</v>
       </c>
       <c r="B97" s="4">
@@ -2131,8 +2122,8 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="9">
+    <row r="98" spans="1:6">
+      <c r="A98" s="4">
         <v>28856</v>
       </c>
       <c r="B98" s="4">
@@ -2148,8 +2139,8 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="9">
+    <row r="99" spans="1:6">
+      <c r="A99" s="4">
         <v>28887</v>
       </c>
       <c r="B99" s="4">
@@ -2165,8 +2156,8 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="9">
+    <row r="100" spans="1:6">
+      <c r="A100" s="4">
         <v>28915</v>
       </c>
       <c r="B100" s="4">
@@ -2182,8 +2173,8 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="9">
+    <row r="101" spans="1:6">
+      <c r="A101" s="4">
         <v>28946</v>
       </c>
       <c r="B101" s="4">
@@ -2199,8 +2190,8 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="9">
+    <row r="102" spans="1:6">
+      <c r="A102" s="4">
         <v>28976</v>
       </c>
       <c r="B102" s="4">
@@ -2216,8 +2207,8 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="9">
+    <row r="103" spans="1:6">
+      <c r="A103" s="4">
         <v>29007</v>
       </c>
       <c r="B103" s="4">
@@ -2233,8 +2224,8 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="9">
+    <row r="104" spans="1:6">
+      <c r="A104" s="4">
         <v>29037</v>
       </c>
       <c r="B104" s="4">
@@ -2250,8 +2241,8 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="9">
+    <row r="105" spans="1:6">
+      <c r="A105" s="4">
         <v>29068</v>
       </c>
       <c r="B105" s="4">
@@ -2267,8 +2258,8 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="9">
+    <row r="106" spans="1:6">
+      <c r="A106" s="4">
         <v>29099</v>
       </c>
       <c r="B106" s="4">
@@ -2284,8 +2275,8 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="9">
+    <row r="107" spans="1:6">
+      <c r="A107" s="4">
         <v>29129</v>
       </c>
       <c r="B107" s="4">
@@ -2301,8 +2292,8 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="9">
+    <row r="108" spans="1:6">
+      <c r="A108" s="4">
         <v>29160</v>
       </c>
       <c r="B108" s="4">
@@ -2318,8 +2309,8 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="9">
+    <row r="109" spans="1:6">
+      <c r="A109" s="4">
         <v>29190</v>
       </c>
       <c r="B109" s="4">
@@ -2335,8 +2326,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="9">
+    <row r="110" spans="1:6">
+      <c r="A110" s="4">
         <v>29221</v>
       </c>
       <c r="B110" s="4">
@@ -2352,8 +2343,8 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="9">
+    <row r="111" spans="1:6">
+      <c r="A111" s="4">
         <v>29252</v>
       </c>
       <c r="B111" s="4">
@@ -2369,8 +2360,8 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="9">
+    <row r="112" spans="1:6">
+      <c r="A112" s="4">
         <v>29281</v>
       </c>
       <c r="B112" s="4">
@@ -2386,8 +2377,8 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="9">
+    <row r="113" spans="1:6">
+      <c r="A113" s="4">
         <v>29312</v>
       </c>
       <c r="B113" s="4">
@@ -2403,8 +2394,8 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="9">
+    <row r="114" spans="1:6">
+      <c r="A114" s="4">
         <v>29342</v>
       </c>
       <c r="B114" s="4">
@@ -2420,8 +2411,8 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="9">
+    <row r="115" spans="1:6">
+      <c r="A115" s="4">
         <v>29373</v>
       </c>
       <c r="B115" s="4">
@@ -2437,8 +2428,8 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="9">
+    <row r="116" spans="1:6">
+      <c r="A116" s="4">
         <v>29403</v>
       </c>
       <c r="B116" s="4">
@@ -2454,8 +2445,8 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="9">
+    <row r="117" spans="1:6">
+      <c r="A117" s="4">
         <v>29434</v>
       </c>
       <c r="B117" s="4">
@@ -2471,8 +2462,8 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="9">
+    <row r="118" spans="1:6">
+      <c r="A118" s="4">
         <v>29465</v>
       </c>
       <c r="B118" s="4">
@@ -2488,8 +2479,8 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="9">
+    <row r="119" spans="1:6">
+      <c r="A119" s="4">
         <v>29495</v>
       </c>
       <c r="B119" s="4">
@@ -2505,8 +2496,8 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="9">
+    <row r="120" spans="1:6">
+      <c r="A120" s="4">
         <v>29526</v>
       </c>
       <c r="B120" s="4">
@@ -2522,8 +2513,8 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="9">
+    <row r="121" spans="1:6">
+      <c r="A121" s="4">
         <v>29556</v>
       </c>
       <c r="B121" s="4">
@@ -2539,8 +2530,8 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="9">
+    <row r="122" spans="1:6">
+      <c r="A122" s="4">
         <v>29587</v>
       </c>
       <c r="B122" s="4">
@@ -2556,8 +2547,8 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="9">
+    <row r="123" spans="1:6">
+      <c r="A123" s="4">
         <v>29618</v>
       </c>
       <c r="B123" s="4">
@@ -2573,8 +2564,8 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="9">
+    <row r="124" spans="1:6">
+      <c r="A124" s="4">
         <v>29646</v>
       </c>
       <c r="B124" s="4">
@@ -2590,8 +2581,8 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="9">
+    <row r="125" spans="1:6">
+      <c r="A125" s="4">
         <v>29677</v>
       </c>
       <c r="B125" s="4">
@@ -2607,8 +2598,8 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="9">
+    <row r="126" spans="1:6">
+      <c r="A126" s="4">
         <v>29707</v>
       </c>
       <c r="B126" s="4">
@@ -2624,8 +2615,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="9">
+    <row r="127" spans="1:6">
+      <c r="A127" s="4">
         <v>29738</v>
       </c>
       <c r="B127" s="4">
@@ -2641,8 +2632,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="9">
+    <row r="128" spans="1:6">
+      <c r="A128" s="4">
         <v>29768</v>
       </c>
       <c r="B128" s="4">
@@ -2658,8 +2649,8 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="9">
+    <row r="129" spans="1:6">
+      <c r="A129" s="4">
         <v>29799</v>
       </c>
       <c r="B129" s="4">
@@ -2675,8 +2666,8 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="9">
+    <row r="130" spans="1:6">
+      <c r="A130" s="4">
         <v>29830</v>
       </c>
       <c r="B130" s="4">
@@ -2692,8 +2683,8 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="9">
+    <row r="131" spans="1:6">
+      <c r="A131" s="4">
         <v>29860</v>
       </c>
       <c r="B131" s="4">
@@ -2709,8 +2700,8 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="9">
+    <row r="132" spans="1:6">
+      <c r="A132" s="4">
         <v>29891</v>
       </c>
       <c r="B132" s="4">
@@ -2726,8 +2717,8 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="9">
+    <row r="133" spans="1:6">
+      <c r="A133" s="4">
         <v>29921</v>
       </c>
       <c r="B133" s="4">
@@ -2743,8 +2734,8 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="9">
+    <row r="134" spans="1:6">
+      <c r="A134" s="4">
         <v>29952</v>
       </c>
       <c r="B134" s="4">
@@ -2760,8 +2751,8 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="9">
+    <row r="135" spans="1:6">
+      <c r="A135" s="4">
         <v>29983</v>
       </c>
       <c r="B135" s="4">
@@ -2777,8 +2768,8 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="9">
+    <row r="136" spans="1:6">
+      <c r="A136" s="4">
         <v>30011</v>
       </c>
       <c r="B136" s="4">
@@ -2794,8 +2785,8 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="9">
+    <row r="137" spans="1:6">
+      <c r="A137" s="4">
         <v>30042</v>
       </c>
       <c r="B137" s="4">
@@ -2811,8 +2802,8 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="9">
+    <row r="138" spans="1:6">
+      <c r="A138" s="4">
         <v>30072</v>
       </c>
       <c r="B138" s="4">
@@ -2828,8 +2819,8 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="9">
+    <row r="139" spans="1:6">
+      <c r="A139" s="4">
         <v>30103</v>
       </c>
       <c r="B139" s="4">
@@ -2845,8 +2836,8 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="9">
+    <row r="140" spans="1:6">
+      <c r="A140" s="4">
         <v>30133</v>
       </c>
       <c r="B140" s="4">
@@ -2862,8 +2853,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="9">
+    <row r="141" spans="1:6">
+      <c r="A141" s="4">
         <v>30164</v>
       </c>
       <c r="B141" s="4">
@@ -2879,8 +2870,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="9">
+    <row r="142" spans="1:6">
+      <c r="A142" s="4">
         <v>30195</v>
       </c>
       <c r="B142" s="4">
@@ -2896,8 +2887,8 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="9">
+    <row r="143" spans="1:6">
+      <c r="A143" s="4">
         <v>30225</v>
       </c>
       <c r="B143" s="4">
@@ -2913,8 +2904,8 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="9">
+    <row r="144" spans="1:6">
+      <c r="A144" s="4">
         <v>30256</v>
       </c>
       <c r="B144" s="4">
@@ -2930,8 +2921,8 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="9">
+    <row r="145" spans="1:6">
+      <c r="A145" s="4">
         <v>30286</v>
       </c>
       <c r="B145" s="4">
@@ -2947,8 +2938,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="9">
+    <row r="146" spans="1:6">
+      <c r="A146" s="4">
         <v>30317</v>
       </c>
       <c r="B146" s="4">
@@ -2964,8 +2955,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="9">
+    <row r="147" spans="1:6">
+      <c r="A147" s="4">
         <v>30348</v>
       </c>
       <c r="B147" s="4">
@@ -2981,8 +2972,8 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="9">
+    <row r="148" spans="1:6">
+      <c r="A148" s="4">
         <v>30376</v>
       </c>
       <c r="B148" s="4">
@@ -2998,8 +2989,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="9">
+    <row r="149" spans="1:6">
+      <c r="A149" s="4">
         <v>30407</v>
       </c>
       <c r="B149" s="4">
@@ -3015,8 +3006,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="9">
+    <row r="150" spans="1:6">
+      <c r="A150" s="4">
         <v>30437</v>
       </c>
       <c r="B150" s="4">
@@ -3032,8 +3023,8 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="9">
+    <row r="151" spans="1:6">
+      <c r="A151" s="4">
         <v>30468</v>
       </c>
       <c r="B151" s="4">
@@ -3049,8 +3040,8 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="9">
+    <row r="152" spans="1:6">
+      <c r="A152" s="4">
         <v>30498</v>
       </c>
       <c r="B152" s="4">
@@ -3066,8 +3057,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="9">
+    <row r="153" spans="1:6">
+      <c r="A153" s="4">
         <v>30529</v>
       </c>
       <c r="B153" s="4">
@@ -3083,8 +3074,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="9">
+    <row r="154" spans="1:6">
+      <c r="A154" s="4">
         <v>30560</v>
       </c>
       <c r="B154" s="4">
@@ -3100,8 +3091,8 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="9">
+    <row r="155" spans="1:6">
+      <c r="A155" s="4">
         <v>30590</v>
       </c>
       <c r="B155" s="4">
@@ -3117,8 +3108,8 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="9">
+    <row r="156" spans="1:6">
+      <c r="A156" s="4">
         <v>30621</v>
       </c>
       <c r="B156" s="4">
@@ -3134,8 +3125,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="9">
+    <row r="157" spans="1:6">
+      <c r="A157" s="4">
         <v>30651</v>
       </c>
       <c r="B157" s="4">
@@ -3151,8 +3142,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="9">
+    <row r="158" spans="1:6">
+      <c r="A158" s="4">
         <v>30682</v>
       </c>
       <c r="B158" s="4">
@@ -3168,8 +3159,8 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="9">
+    <row r="159" spans="1:6">
+      <c r="A159" s="4">
         <v>30713</v>
       </c>
       <c r="B159" s="4">
@@ -3185,8 +3176,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="9">
+    <row r="160" spans="1:6">
+      <c r="A160" s="4">
         <v>30742</v>
       </c>
       <c r="B160" s="4">
@@ -3202,8 +3193,8 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="9">
+    <row r="161" spans="1:6">
+      <c r="A161" s="4">
         <v>30773</v>
       </c>
       <c r="B161" s="4">
@@ -3219,8 +3210,8 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="9">
+    <row r="162" spans="1:6">
+      <c r="A162" s="4">
         <v>30803</v>
       </c>
       <c r="B162" s="4">
@@ -3236,8 +3227,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="9">
+    <row r="163" spans="1:6">
+      <c r="A163" s="4">
         <v>30834</v>
       </c>
       <c r="B163" s="4">
@@ -3253,8 +3244,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="9">
+    <row r="164" spans="1:6">
+      <c r="A164" s="4">
         <v>30864</v>
       </c>
       <c r="B164" s="4">
@@ -3270,8 +3261,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="9">
+    <row r="165" spans="1:6">
+      <c r="A165" s="4">
         <v>30895</v>
       </c>
       <c r="B165" s="4">
@@ -3287,8 +3278,8 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="9">
+    <row r="166" spans="1:6">
+      <c r="A166" s="4">
         <v>30926</v>
       </c>
       <c r="B166" s="4">
@@ -3304,8 +3295,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="9">
+    <row r="167" spans="1:6">
+      <c r="A167" s="4">
         <v>30956</v>
       </c>
       <c r="B167" s="4">
@@ -3321,8 +3312,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="9">
+    <row r="168" spans="1:6">
+      <c r="A168" s="4">
         <v>30987</v>
       </c>
       <c r="B168" s="4">
@@ -3338,8 +3329,8 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="9">
+    <row r="169" spans="1:6">
+      <c r="A169" s="4">
         <v>31017</v>
       </c>
       <c r="B169" s="4">
@@ -3355,8 +3346,8 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="9">
+    <row r="170" spans="1:6">
+      <c r="A170" s="4">
         <v>31048</v>
       </c>
       <c r="B170" s="4">
@@ -3372,8 +3363,8 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="9">
+    <row r="171" spans="1:6">
+      <c r="A171" s="4">
         <v>31079</v>
       </c>
       <c r="B171" s="4">
@@ -3389,8 +3380,8 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="9">
+    <row r="172" spans="1:6">
+      <c r="A172" s="4">
         <v>31107</v>
       </c>
       <c r="B172" s="4">
@@ -3406,8 +3397,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="9">
+    <row r="173" spans="1:6">
+      <c r="A173" s="4">
         <v>31138</v>
       </c>
       <c r="B173" s="4">
@@ -3423,8 +3414,8 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="9">
+    <row r="174" spans="1:6">
+      <c r="A174" s="4">
         <v>31168</v>
       </c>
       <c r="B174" s="4">
@@ -3440,8 +3431,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="9">
+    <row r="175" spans="1:6">
+      <c r="A175" s="4">
         <v>31199</v>
       </c>
       <c r="B175" s="4">
@@ -3457,8 +3448,8 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="9">
+    <row r="176" spans="1:6">
+      <c r="A176" s="4">
         <v>31229</v>
       </c>
       <c r="B176" s="4">
@@ -3474,8 +3465,8 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" s="9">
+    <row r="177" spans="1:6">
+      <c r="A177" s="4">
         <v>31260</v>
       </c>
       <c r="B177" s="4">
@@ -3491,8 +3482,8 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="9">
+    <row r="178" spans="1:6">
+      <c r="A178" s="4">
         <v>31291</v>
       </c>
       <c r="B178" s="4">
@@ -3508,8 +3499,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" s="9">
+    <row r="179" spans="1:6">
+      <c r="A179" s="4">
         <v>31321</v>
       </c>
       <c r="B179" s="4">
@@ -3525,8 +3516,8 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="9">
+    <row r="180" spans="1:6">
+      <c r="A180" s="4">
         <v>31352</v>
       </c>
       <c r="B180" s="4">
@@ -3542,8 +3533,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="9">
+    <row r="181" spans="1:6">
+      <c r="A181" s="4">
         <v>31382</v>
       </c>
       <c r="B181" s="4">
@@ -3559,8 +3550,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" s="9">
+    <row r="182" spans="1:6">
+      <c r="A182" s="4">
         <v>31413</v>
       </c>
       <c r="B182" s="4">
@@ -3576,8 +3567,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="9">
+    <row r="183" spans="1:6">
+      <c r="A183" s="4">
         <v>31444</v>
       </c>
       <c r="B183" s="4">
@@ -3593,8 +3584,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="9">
+    <row r="184" spans="1:6">
+      <c r="A184" s="4">
         <v>31472</v>
       </c>
       <c r="B184" s="4">
@@ -3610,8 +3601,8 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="9">
+    <row r="185" spans="1:6">
+      <c r="A185" s="4">
         <v>31503</v>
       </c>
       <c r="B185" s="4">
@@ -3627,8 +3618,8 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="9">
+    <row r="186" spans="1:6">
+      <c r="A186" s="4">
         <v>31533</v>
       </c>
       <c r="B186" s="4">
@@ -3644,8 +3635,8 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="9">
+    <row r="187" spans="1:6">
+      <c r="A187" s="4">
         <v>31564</v>
       </c>
       <c r="B187" s="4">
@@ -3661,8 +3652,8 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="9">
+    <row r="188" spans="1:6">
+      <c r="A188" s="4">
         <v>31594</v>
       </c>
       <c r="B188" s="4">
@@ -3678,8 +3669,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="9">
+    <row r="189" spans="1:6">
+      <c r="A189" s="4">
         <v>31625</v>
       </c>
       <c r="B189" s="4">
@@ -3695,8 +3686,8 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="9">
+    <row r="190" spans="1:6">
+      <c r="A190" s="4">
         <v>31656</v>
       </c>
       <c r="B190" s="4">
@@ -3712,8 +3703,8 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="9">
+    <row r="191" spans="1:6">
+      <c r="A191" s="4">
         <v>31686</v>
       </c>
       <c r="B191" s="4">
@@ -3729,8 +3720,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="9">
+    <row r="192" spans="1:6">
+      <c r="A192" s="4">
         <v>31717</v>
       </c>
       <c r="B192" s="4">
@@ -3746,8 +3737,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="9">
+    <row r="193" spans="1:6">
+      <c r="A193" s="4">
         <v>31747</v>
       </c>
       <c r="B193" s="4">
@@ -3763,8 +3754,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="9">
+    <row r="194" spans="1:6">
+      <c r="A194" s="4">
         <v>31778</v>
       </c>
       <c r="B194" s="4">
@@ -3780,8 +3771,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" s="9">
+    <row r="195" spans="1:6">
+      <c r="A195" s="4">
         <v>31809</v>
       </c>
       <c r="B195" s="4">
@@ -3797,8 +3788,8 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="9">
+    <row r="196" spans="1:6">
+      <c r="A196" s="4">
         <v>31837</v>
       </c>
       <c r="B196" s="4">
@@ -3814,8 +3805,8 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="9">
+    <row r="197" spans="1:6">
+      <c r="A197" s="4">
         <v>31868</v>
       </c>
       <c r="B197" s="4">
@@ -3831,8 +3822,8 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="9">
+    <row r="198" spans="1:6">
+      <c r="A198" s="4">
         <v>31898</v>
       </c>
       <c r="B198" s="4">
@@ -3848,8 +3839,8 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="9">
+    <row r="199" spans="1:6">
+      <c r="A199" s="4">
         <v>31929</v>
       </c>
       <c r="B199" s="4">
@@ -3865,8 +3856,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="9">
+    <row r="200" spans="1:6">
+      <c r="A200" s="4">
         <v>31959</v>
       </c>
       <c r="B200" s="4">
@@ -3882,8 +3873,8 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="9">
+    <row r="201" spans="1:6">
+      <c r="A201" s="4">
         <v>31990</v>
       </c>
       <c r="B201" s="4">
@@ -3899,8 +3890,8 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="9">
+    <row r="202" spans="1:6">
+      <c r="A202" s="4">
         <v>32021</v>
       </c>
       <c r="B202" s="4">
@@ -3916,8 +3907,8 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="9">
+    <row r="203" spans="1:6">
+      <c r="A203" s="4">
         <v>32051</v>
       </c>
       <c r="B203" s="4">
@@ -3933,8 +3924,8 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="9">
+    <row r="204" spans="1:6">
+      <c r="A204" s="4">
         <v>32082</v>
       </c>
       <c r="B204" s="4">
@@ -3950,8 +3941,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="9">
+    <row r="205" spans="1:6">
+      <c r="A205" s="4">
         <v>32112</v>
       </c>
       <c r="B205" s="4">
@@ -3967,8 +3958,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="9">
+    <row r="206" spans="1:6">
+      <c r="A206" s="4">
         <v>32143</v>
       </c>
       <c r="B206" s="4">
@@ -3984,8 +3975,8 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="9">
+    <row r="207" spans="1:6">
+      <c r="A207" s="4">
         <v>32174</v>
       </c>
       <c r="B207" s="4">
@@ -4001,8 +3992,8 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="9">
+    <row r="208" spans="1:6">
+      <c r="A208" s="4">
         <v>32203</v>
       </c>
       <c r="B208" s="4">
@@ -4018,8 +4009,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="9">
+    <row r="209" spans="1:6">
+      <c r="A209" s="4">
         <v>32234</v>
       </c>
       <c r="B209" s="4">
@@ -4035,8 +4026,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="9">
+    <row r="210" spans="1:6">
+      <c r="A210" s="4">
         <v>32264</v>
       </c>
       <c r="B210" s="4">
@@ -4052,8 +4043,8 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="9">
+    <row r="211" spans="1:6">
+      <c r="A211" s="4">
         <v>32295</v>
       </c>
       <c r="B211" s="4">
@@ -4069,8 +4060,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="9">
+    <row r="212" spans="1:6">
+      <c r="A212" s="4">
         <v>32325</v>
       </c>
       <c r="B212" s="4">
@@ -4086,8 +4077,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" s="9">
+    <row r="213" spans="1:6">
+      <c r="A213" s="4">
         <v>32356</v>
       </c>
       <c r="B213" s="4">
@@ -4103,8 +4094,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" s="9">
+    <row r="214" spans="1:6">
+      <c r="A214" s="4">
         <v>32387</v>
       </c>
       <c r="B214" s="4">
@@ -4120,8 +4111,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="9">
+    <row r="215" spans="1:6">
+      <c r="A215" s="4">
         <v>32417</v>
       </c>
       <c r="B215" s="4">
@@ -4137,8 +4128,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="9">
+    <row r="216" spans="1:6">
+      <c r="A216" s="4">
         <v>32448</v>
       </c>
       <c r="B216" s="4">
@@ -4154,8 +4145,8 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217" s="9">
+    <row r="217" spans="1:6">
+      <c r="A217" s="4">
         <v>32478</v>
       </c>
       <c r="B217" s="4">
@@ -4171,8 +4162,8 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" s="9">
+    <row r="218" spans="1:6">
+      <c r="A218" s="4">
         <v>32509</v>
       </c>
       <c r="B218" s="4">
@@ -4188,8 +4179,8 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" s="9">
+    <row r="219" spans="1:6">
+      <c r="A219" s="4">
         <v>32540</v>
       </c>
       <c r="B219" s="4">
@@ -4205,8 +4196,8 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" s="9">
+    <row r="220" spans="1:6">
+      <c r="A220" s="4">
         <v>32568</v>
       </c>
       <c r="B220" s="4">
@@ -4222,8 +4213,8 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="9">
+    <row r="221" spans="1:6">
+      <c r="A221" s="4">
         <v>32599</v>
       </c>
       <c r="B221" s="4">
@@ -4239,8 +4230,8 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" s="9">
+    <row r="222" spans="1:6">
+      <c r="A222" s="4">
         <v>32629</v>
       </c>
       <c r="B222" s="4">
@@ -4256,8 +4247,8 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" s="9">
+    <row r="223" spans="1:6">
+      <c r="A223" s="4">
         <v>32660</v>
       </c>
       <c r="B223" s="4">
@@ -4273,8 +4264,8 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" s="9">
+    <row r="224" spans="1:6">
+      <c r="A224" s="4">
         <v>32690</v>
       </c>
       <c r="B224" s="4">
@@ -4290,8 +4281,8 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" s="9">
+    <row r="225" spans="1:6">
+      <c r="A225" s="4">
         <v>32721</v>
       </c>
       <c r="B225" s="4">
@@ -4307,8 +4298,8 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226" s="9">
+    <row r="226" spans="1:6">
+      <c r="A226" s="4">
         <v>32752</v>
       </c>
       <c r="B226" s="4">
@@ -4324,8 +4315,8 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227" s="9">
+    <row r="227" spans="1:6">
+      <c r="A227" s="4">
         <v>32782</v>
       </c>
       <c r="B227" s="4">
@@ -4341,8 +4332,8 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A228" s="9">
+    <row r="228" spans="1:6">
+      <c r="A228" s="4">
         <v>32813</v>
       </c>
       <c r="B228" s="4">
@@ -4358,8 +4349,8 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A229" s="9">
+    <row r="229" spans="1:6">
+      <c r="A229" s="4">
         <v>32843</v>
       </c>
       <c r="B229" s="4">
@@ -4375,8 +4366,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230" s="9">
+    <row r="230" spans="1:6">
+      <c r="A230" s="4">
         <v>32874</v>
       </c>
       <c r="B230" s="4">
@@ -4392,8 +4383,8 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A231" s="9">
+    <row r="231" spans="1:6">
+      <c r="A231" s="4">
         <v>32905</v>
       </c>
       <c r="B231" s="4">
@@ -4409,8 +4400,8 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A232" s="9">
+    <row r="232" spans="1:6">
+      <c r="A232" s="4">
         <v>32933</v>
       </c>
       <c r="B232" s="4">
@@ -4426,8 +4417,8 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" s="9">
+    <row r="233" spans="1:6">
+      <c r="A233" s="4">
         <v>32964</v>
       </c>
       <c r="B233" s="4">
@@ -4443,8 +4434,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" s="9">
+    <row r="234" spans="1:6">
+      <c r="A234" s="4">
         <v>32994</v>
       </c>
       <c r="B234" s="4">
@@ -4460,8 +4451,8 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="9">
+    <row r="235" spans="1:6">
+      <c r="A235" s="4">
         <v>33025</v>
       </c>
       <c r="B235" s="4">
@@ -4477,8 +4468,8 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236" s="9">
+    <row r="236" spans="1:6">
+      <c r="A236" s="4">
         <v>33055</v>
       </c>
       <c r="B236" s="4">
@@ -4494,8 +4485,8 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A237" s="9">
+    <row r="237" spans="1:6">
+      <c r="A237" s="4">
         <v>33086</v>
       </c>
       <c r="B237" s="4">
@@ -4511,8 +4502,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A238" s="9">
+    <row r="238" spans="1:6">
+      <c r="A238" s="4">
         <v>33117</v>
       </c>
       <c r="B238" s="4">
@@ -4528,8 +4519,8 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239" s="9">
+    <row r="239" spans="1:6">
+      <c r="A239" s="4">
         <v>33147</v>
       </c>
       <c r="B239" s="4">
@@ -4545,8 +4536,8 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A240" s="9">
+    <row r="240" spans="1:6">
+      <c r="A240" s="4">
         <v>33178</v>
       </c>
       <c r="B240" s="4">
@@ -4562,8 +4553,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A241" s="9">
+    <row r="241" spans="1:6">
+      <c r="A241" s="4">
         <v>33208</v>
       </c>
       <c r="B241" s="4">
@@ -4579,8 +4570,8 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A242" s="9">
+    <row r="242" spans="1:6">
+      <c r="A242" s="4">
         <v>33239</v>
       </c>
       <c r="B242" s="4">
@@ -4596,8 +4587,8 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A243" s="9">
+    <row r="243" spans="1:6">
+      <c r="A243" s="4">
         <v>33270</v>
       </c>
       <c r="B243" s="4">
@@ -4613,8 +4604,8 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A244" s="9">
+    <row r="244" spans="1:6">
+      <c r="A244" s="4">
         <v>33298</v>
       </c>
       <c r="B244" s="4">
@@ -4630,8 +4621,8 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A245" s="9">
+    <row r="245" spans="1:6">
+      <c r="A245" s="4">
         <v>33329</v>
       </c>
       <c r="B245" s="4">
@@ -4647,8 +4638,8 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A246" s="9">
+    <row r="246" spans="1:6">
+      <c r="A246" s="4">
         <v>33359</v>
       </c>
       <c r="B246" s="4">
@@ -4664,8 +4655,8 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A247" s="9">
+    <row r="247" spans="1:6">
+      <c r="A247" s="4">
         <v>33390</v>
       </c>
       <c r="B247" s="4">
@@ -4681,8 +4672,8 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A248" s="9">
+    <row r="248" spans="1:6">
+      <c r="A248" s="4">
         <v>33420</v>
       </c>
       <c r="B248" s="4">
@@ -4698,8 +4689,8 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A249" s="9">
+    <row r="249" spans="1:6">
+      <c r="A249" s="4">
         <v>33451</v>
       </c>
       <c r="B249" s="4">
@@ -4715,8 +4706,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A250" s="9">
+    <row r="250" spans="1:6">
+      <c r="A250" s="4">
         <v>33482</v>
       </c>
       <c r="B250" s="4">
@@ -4732,8 +4723,8 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A251" s="9">
+    <row r="251" spans="1:6">
+      <c r="A251" s="4">
         <v>33512</v>
       </c>
       <c r="B251" s="4">
@@ -4749,8 +4740,8 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A252" s="9">
+    <row r="252" spans="1:6">
+      <c r="A252" s="4">
         <v>33543</v>
       </c>
       <c r="B252" s="4">
@@ -4766,8 +4757,8 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A253" s="9">
+    <row r="253" spans="1:6">
+      <c r="A253" s="4">
         <v>33573</v>
       </c>
       <c r="B253" s="4">
@@ -4783,8 +4774,8 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A254" s="9">
+    <row r="254" spans="1:6">
+      <c r="A254" s="4">
         <v>33604</v>
       </c>
       <c r="B254" s="4">
@@ -4800,8 +4791,8 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A255" s="9">
+    <row r="255" spans="1:6">
+      <c r="A255" s="4">
         <v>33635</v>
       </c>
       <c r="B255" s="4">
@@ -4817,8 +4808,8 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256" s="9">
+    <row r="256" spans="1:6">
+      <c r="A256" s="4">
         <v>33664</v>
       </c>
       <c r="B256" s="4">
@@ -4834,8 +4825,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A257" s="9">
+    <row r="257" spans="1:6">
+      <c r="A257" s="4">
         <v>33695</v>
       </c>
       <c r="B257" s="4">
@@ -4851,8 +4842,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A258" s="9">
+    <row r="258" spans="1:6">
+      <c r="A258" s="4">
         <v>33725</v>
       </c>
       <c r="B258" s="4">
@@ -4868,8 +4859,8 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A259" s="9">
+    <row r="259" spans="1:6">
+      <c r="A259" s="4">
         <v>33756</v>
       </c>
       <c r="B259" s="4">
@@ -4885,8 +4876,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A260" s="9">
+    <row r="260" spans="1:6">
+      <c r="A260" s="4">
         <v>33786</v>
       </c>
       <c r="B260" s="4">
@@ -4902,8 +4893,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A261" s="9">
+    <row r="261" spans="1:6">
+      <c r="A261" s="4">
         <v>33817</v>
       </c>
       <c r="B261" s="4">
@@ -4919,8 +4910,8 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A262" s="9">
+    <row r="262" spans="1:6">
+      <c r="A262" s="4">
         <v>33848</v>
       </c>
       <c r="B262" s="4">
@@ -4936,8 +4927,8 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A263" s="9">
+    <row r="263" spans="1:6">
+      <c r="A263" s="4">
         <v>33878</v>
       </c>
       <c r="B263" s="4">
@@ -4953,8 +4944,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A264" s="9">
+    <row r="264" spans="1:6">
+      <c r="A264" s="4">
         <v>33909</v>
       </c>
       <c r="B264" s="4">
@@ -4970,8 +4961,8 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A265" s="9">
+    <row r="265" spans="1:6">
+      <c r="A265" s="4">
         <v>33939</v>
       </c>
       <c r="B265" s="4">
@@ -4987,8 +4978,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A266" s="9">
+    <row r="266" spans="1:6">
+      <c r="A266" s="4">
         <v>33970</v>
       </c>
       <c r="B266" s="4">
@@ -5004,8 +4995,8 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A267" s="9">
+    <row r="267" spans="1:6">
+      <c r="A267" s="4">
         <v>34001</v>
       </c>
       <c r="B267" s="4">
@@ -5021,8 +5012,8 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A268" s="9">
+    <row r="268" spans="1:6">
+      <c r="A268" s="4">
         <v>34029</v>
       </c>
       <c r="B268" s="4">
@@ -5038,8 +5029,8 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A269" s="9">
+    <row r="269" spans="1:6">
+      <c r="A269" s="4">
         <v>34060</v>
       </c>
       <c r="B269" s="4">
@@ -5055,8 +5046,8 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A270" s="9">
+    <row r="270" spans="1:6">
+      <c r="A270" s="4">
         <v>34090</v>
       </c>
       <c r="B270" s="4">
@@ -5072,8 +5063,8 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A271" s="9">
+    <row r="271" spans="1:6">
+      <c r="A271" s="4">
         <v>34121</v>
       </c>
       <c r="B271" s="4">
@@ -5089,8 +5080,8 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A272" s="9">
+    <row r="272" spans="1:6">
+      <c r="A272" s="4">
         <v>34151</v>
       </c>
       <c r="B272" s="4">
@@ -5106,8 +5097,8 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273" s="9">
+    <row r="273" spans="1:6">
+      <c r="A273" s="4">
         <v>34182</v>
       </c>
       <c r="B273" s="4">
@@ -5123,8 +5114,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274" s="9">
+    <row r="274" spans="1:6">
+      <c r="A274" s="4">
         <v>34213</v>
       </c>
       <c r="B274" s="4">
@@ -5140,8 +5131,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275" s="9">
+    <row r="275" spans="1:6">
+      <c r="A275" s="4">
         <v>34243</v>
       </c>
       <c r="B275" s="4">
@@ -5157,8 +5148,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276" s="9">
+    <row r="276" spans="1:6">
+      <c r="A276" s="4">
         <v>34274</v>
       </c>
       <c r="B276" s="4">
@@ -5174,8 +5165,8 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A277" s="9">
+    <row r="277" spans="1:6">
+      <c r="A277" s="4">
         <v>34304</v>
       </c>
       <c r="B277" s="4">
@@ -5191,8 +5182,8 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A278" s="9">
+    <row r="278" spans="1:6">
+      <c r="A278" s="4">
         <v>34335</v>
       </c>
       <c r="B278" s="4">
@@ -5208,8 +5199,8 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A279" s="9">
+    <row r="279" spans="1:6">
+      <c r="A279" s="4">
         <v>34366</v>
       </c>
       <c r="B279" s="4">
@@ -5225,8 +5216,8 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A280" s="9">
+    <row r="280" spans="1:6">
+      <c r="A280" s="4">
         <v>34394</v>
       </c>
       <c r="B280" s="4">
@@ -5242,8 +5233,8 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A281" s="9">
+    <row r="281" spans="1:6">
+      <c r="A281" s="4">
         <v>34425</v>
       </c>
       <c r="B281" s="4">
@@ -5259,8 +5250,8 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A282" s="9">
+    <row r="282" spans="1:6">
+      <c r="A282" s="4">
         <v>34455</v>
       </c>
       <c r="B282" s="4">
@@ -5276,8 +5267,8 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A283" s="9">
+    <row r="283" spans="1:6">
+      <c r="A283" s="4">
         <v>34486</v>
       </c>
       <c r="B283" s="4">
@@ -5293,8 +5284,8 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A284" s="9">
+    <row r="284" spans="1:6">
+      <c r="A284" s="4">
         <v>34516</v>
       </c>
       <c r="B284" s="4">
@@ -5310,8 +5301,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A285" s="9">
+    <row r="285" spans="1:6">
+      <c r="A285" s="4">
         <v>34547</v>
       </c>
       <c r="B285" s="4">
@@ -5327,8 +5318,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A286" s="9">
+    <row r="286" spans="1:6">
+      <c r="A286" s="4">
         <v>34578</v>
       </c>
       <c r="B286" s="4">
@@ -5344,8 +5335,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A287" s="9">
+    <row r="287" spans="1:6">
+      <c r="A287" s="4">
         <v>34608</v>
       </c>
       <c r="B287" s="4">
@@ -5361,8 +5352,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A288" s="9">
+    <row r="288" spans="1:6">
+      <c r="A288" s="4">
         <v>34639</v>
       </c>
       <c r="B288" s="4">
@@ -5378,8 +5369,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A289" s="9">
+    <row r="289" spans="1:6">
+      <c r="A289" s="4">
         <v>34669</v>
       </c>
       <c r="B289" s="4">
@@ -5395,8 +5386,8 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A290" s="9">
+    <row r="290" spans="1:6">
+      <c r="A290" s="4">
         <v>34700</v>
       </c>
       <c r="B290" s="4">
@@ -5412,8 +5403,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A291" s="9">
+    <row r="291" spans="1:6">
+      <c r="A291" s="4">
         <v>34731</v>
       </c>
       <c r="B291" s="4">
@@ -5429,8 +5420,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A292" s="9">
+    <row r="292" spans="1:6">
+      <c r="A292" s="4">
         <v>34759</v>
       </c>
       <c r="B292" s="4">
@@ -5446,8 +5437,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A293" s="9">
+    <row r="293" spans="1:6">
+      <c r="A293" s="4">
         <v>34790</v>
       </c>
       <c r="B293" s="4">
@@ -5463,8 +5454,8 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A294" s="9">
+    <row r="294" spans="1:6">
+      <c r="A294" s="4">
         <v>34820</v>
       </c>
       <c r="B294" s="4">
@@ -5480,8 +5471,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A295" s="9">
+    <row r="295" spans="1:6">
+      <c r="A295" s="4">
         <v>34851</v>
       </c>
       <c r="B295" s="4">
@@ -5497,8 +5488,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A296" s="9">
+    <row r="296" spans="1:6">
+      <c r="A296" s="4">
         <v>34881</v>
       </c>
       <c r="B296" s="4">
@@ -5514,8 +5505,8 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A297" s="9">
+    <row r="297" spans="1:6">
+      <c r="A297" s="4">
         <v>34912</v>
       </c>
       <c r="B297" s="4">
@@ -5531,8 +5522,8 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A298" s="9">
+    <row r="298" spans="1:6">
+      <c r="A298" s="4">
         <v>34943</v>
       </c>
       <c r="B298" s="4">
@@ -5548,8 +5539,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A299" s="9">
+    <row r="299" spans="1:6">
+      <c r="A299" s="4">
         <v>34973</v>
       </c>
       <c r="B299" s="4">
@@ -5565,8 +5556,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A300" s="9">
+    <row r="300" spans="1:6">
+      <c r="A300" s="4">
         <v>35004</v>
       </c>
       <c r="B300" s="4">
@@ -5582,8 +5573,8 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301" s="9">
+    <row r="301" spans="1:6">
+      <c r="A301" s="4">
         <v>35034</v>
       </c>
       <c r="B301" s="4">
@@ -5599,8 +5590,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A302" s="9">
+    <row r="302" spans="1:6">
+      <c r="A302" s="4">
         <v>35065</v>
       </c>
       <c r="B302" s="4">
@@ -5616,8 +5607,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A303" s="9">
+    <row r="303" spans="1:6">
+      <c r="A303" s="4">
         <v>35096</v>
       </c>
       <c r="B303" s="4">
@@ -5633,8 +5624,8 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A304" s="9">
+    <row r="304" spans="1:6">
+      <c r="A304" s="4">
         <v>35125</v>
       </c>
       <c r="B304" s="4">
@@ -5650,8 +5641,8 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A305" s="9">
+    <row r="305" spans="1:6">
+      <c r="A305" s="4">
         <v>35156</v>
       </c>
       <c r="B305" s="4">
@@ -5667,8 +5658,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A306" s="9">
+    <row r="306" spans="1:6">
+      <c r="A306" s="4">
         <v>35186</v>
       </c>
       <c r="B306" s="4">
@@ -5684,8 +5675,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A307" s="9">
+    <row r="307" spans="1:6">
+      <c r="A307" s="4">
         <v>35217</v>
       </c>
       <c r="B307" s="4">
@@ -5701,8 +5692,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A308" s="9">
+    <row r="308" spans="1:6">
+      <c r="A308" s="4">
         <v>35247</v>
       </c>
       <c r="B308" s="4">
@@ -5718,8 +5709,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A309" s="9">
+    <row r="309" spans="1:6">
+      <c r="A309" s="4">
         <v>35278</v>
       </c>
       <c r="B309" s="4">
@@ -5735,8 +5726,8 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A310" s="9">
+    <row r="310" spans="1:6">
+      <c r="A310" s="4">
         <v>35309</v>
       </c>
       <c r="B310" s="4">
@@ -5752,8 +5743,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A311" s="9">
+    <row r="311" spans="1:6">
+      <c r="A311" s="4">
         <v>35339</v>
       </c>
       <c r="B311" s="4">
@@ -5769,8 +5760,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A312" s="9">
+    <row r="312" spans="1:6">
+      <c r="A312" s="4">
         <v>35370</v>
       </c>
       <c r="B312" s="4">
@@ -5786,8 +5777,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A313" s="9">
+    <row r="313" spans="1:6">
+      <c r="A313" s="4">
         <v>35400</v>
       </c>
       <c r="B313" s="4">
@@ -5803,8 +5794,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A314" s="9">
+    <row r="314" spans="1:6">
+      <c r="A314" s="4">
         <v>35431</v>
       </c>
       <c r="B314" s="4">
@@ -5820,8 +5811,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A315" s="9">
+    <row r="315" spans="1:6">
+      <c r="A315" s="4">
         <v>35462</v>
       </c>
       <c r="B315" s="4">
@@ -5837,8 +5828,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A316" s="9">
+    <row r="316" spans="1:6">
+      <c r="A316" s="4">
         <v>35490</v>
       </c>
       <c r="B316" s="4">
@@ -5854,8 +5845,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A317" s="9">
+    <row r="317" spans="1:6">
+      <c r="A317" s="4">
         <v>35521</v>
       </c>
       <c r="B317" s="4">
@@ -5871,8 +5862,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A318" s="9">
+    <row r="318" spans="1:6">
+      <c r="A318" s="4">
         <v>35551</v>
       </c>
       <c r="B318" s="4">
@@ -5888,8 +5879,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A319" s="9">
+    <row r="319" spans="1:6">
+      <c r="A319" s="4">
         <v>35582</v>
       </c>
       <c r="B319" s="4">
@@ -5905,8 +5896,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A320" s="9">
+    <row r="320" spans="1:6">
+      <c r="A320" s="4">
         <v>35612</v>
       </c>
       <c r="B320" s="4">
@@ -5922,8 +5913,8 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A321" s="9">
+    <row r="321" spans="1:6">
+      <c r="A321" s="4">
         <v>35643</v>
       </c>
       <c r="B321" s="4">
@@ -5939,8 +5930,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A322" s="9">
+    <row r="322" spans="1:6">
+      <c r="A322" s="4">
         <v>35674</v>
       </c>
       <c r="B322" s="4">
@@ -5956,8 +5947,8 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A323" s="9">
+    <row r="323" spans="1:6">
+      <c r="A323" s="4">
         <v>35704</v>
       </c>
       <c r="B323" s="4">
@@ -5973,8 +5964,8 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A324" s="9">
+    <row r="324" spans="1:6">
+      <c r="A324" s="4">
         <v>35735</v>
       </c>
       <c r="B324" s="4">
@@ -5990,8 +5981,8 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A325" s="9">
+    <row r="325" spans="1:6">
+      <c r="A325" s="4">
         <v>35765</v>
       </c>
       <c r="B325" s="4">
@@ -6007,8 +5998,8 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A326" s="9">
+    <row r="326" spans="1:6">
+      <c r="A326" s="4">
         <v>35796</v>
       </c>
       <c r="B326" s="4">
@@ -6024,8 +6015,8 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A327" s="9">
+    <row r="327" spans="1:6">
+      <c r="A327" s="4">
         <v>35827</v>
       </c>
       <c r="B327" s="4">
@@ -6041,8 +6032,8 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A328" s="9">
+    <row r="328" spans="1:6">
+      <c r="A328" s="4">
         <v>35855</v>
       </c>
       <c r="B328" s="4">
@@ -6058,8 +6049,8 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A329" s="9">
+    <row r="329" spans="1:6">
+      <c r="A329" s="4">
         <v>35886</v>
       </c>
       <c r="B329" s="4">
@@ -6075,8 +6066,8 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A330" s="9">
+    <row r="330" spans="1:6">
+      <c r="A330" s="4">
         <v>35916</v>
       </c>
       <c r="B330" s="4">
@@ -6092,8 +6083,8 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A331" s="9">
+    <row r="331" spans="1:6">
+      <c r="A331" s="4">
         <v>35947</v>
       </c>
       <c r="B331" s="4">
@@ -6109,8 +6100,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A332" s="9">
+    <row r="332" spans="1:6">
+      <c r="A332" s="4">
         <v>35977</v>
       </c>
       <c r="B332" s="4">
@@ -6126,8 +6117,8 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A333" s="9">
+    <row r="333" spans="1:6">
+      <c r="A333" s="4">
         <v>36008</v>
       </c>
       <c r="B333" s="4">
@@ -6143,8 +6134,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A334" s="9">
+    <row r="334" spans="1:6">
+      <c r="A334" s="4">
         <v>36039</v>
       </c>
       <c r="B334" s="4">
@@ -6160,8 +6151,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A335" s="9">
+    <row r="335" spans="1:6">
+      <c r="A335" s="4">
         <v>36069</v>
       </c>
       <c r="B335" s="4">
@@ -6177,8 +6168,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A336" s="9">
+    <row r="336" spans="1:6">
+      <c r="A336" s="4">
         <v>36100</v>
       </c>
       <c r="B336" s="4">
@@ -6194,8 +6185,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A337" s="9">
+    <row r="337" spans="1:6">
+      <c r="A337" s="4">
         <v>36130</v>
       </c>
       <c r="B337" s="4">
@@ -6211,8 +6202,8 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A338" s="9">
+    <row r="338" spans="1:6">
+      <c r="A338" s="4">
         <v>36161</v>
       </c>
       <c r="B338" s="4">
@@ -6228,8 +6219,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A339" s="9">
+    <row r="339" spans="1:6">
+      <c r="A339" s="4">
         <v>36192</v>
       </c>
       <c r="B339" s="4">
@@ -6245,8 +6236,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A340" s="9">
+    <row r="340" spans="1:6">
+      <c r="A340" s="4">
         <v>36220</v>
       </c>
       <c r="B340" s="4">
@@ -6262,8 +6253,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A341" s="9">
+    <row r="341" spans="1:6">
+      <c r="A341" s="4">
         <v>36251</v>
       </c>
       <c r="B341" s="4">
@@ -6279,8 +6270,8 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A342" s="9">
+    <row r="342" spans="1:6">
+      <c r="A342" s="4">
         <v>36281</v>
       </c>
       <c r="B342" s="4">
@@ -6296,8 +6287,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A343" s="9">
+    <row r="343" spans="1:6">
+      <c r="A343" s="4">
         <v>36312</v>
       </c>
       <c r="B343" s="4">
@@ -6313,8 +6304,8 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A344" s="9">
+    <row r="344" spans="1:6">
+      <c r="A344" s="4">
         <v>36342</v>
       </c>
       <c r="B344" s="4">
@@ -6330,8 +6321,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A345" s="9">
+    <row r="345" spans="1:6">
+      <c r="A345" s="4">
         <v>36373</v>
       </c>
       <c r="B345" s="4">
@@ -6347,8 +6338,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A346" s="9">
+    <row r="346" spans="1:6">
+      <c r="A346" s="4">
         <v>36404</v>
       </c>
       <c r="B346" s="4">
@@ -6364,8 +6355,8 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A347" s="9">
+    <row r="347" spans="1:6">
+      <c r="A347" s="4">
         <v>36434</v>
       </c>
       <c r="B347" s="4">
@@ -6381,8 +6372,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A348" s="9">
+    <row r="348" spans="1:6">
+      <c r="A348" s="4">
         <v>36465</v>
       </c>
       <c r="B348" s="4">
@@ -6398,8 +6389,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A349" s="9">
+    <row r="349" spans="1:6">
+      <c r="A349" s="4">
         <v>36495</v>
       </c>
       <c r="B349" s="4">
@@ -6415,8 +6406,8 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A350" s="9">
+    <row r="350" spans="1:6">
+      <c r="A350" s="4">
         <v>36526</v>
       </c>
       <c r="B350" s="4">
@@ -6432,8 +6423,8 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A351" s="9">
+    <row r="351" spans="1:6">
+      <c r="A351" s="4">
         <v>36557</v>
       </c>
       <c r="B351" s="4">
@@ -6449,8 +6440,8 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A352" s="9">
+    <row r="352" spans="1:6">
+      <c r="A352" s="4">
         <v>36586</v>
       </c>
       <c r="B352" s="4">
@@ -6466,8 +6457,8 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A353" s="9">
+    <row r="353" spans="1:6">
+      <c r="A353" s="4">
         <v>36617</v>
       </c>
       <c r="B353" s="4">
@@ -6483,8 +6474,8 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A354" s="9">
+    <row r="354" spans="1:6">
+      <c r="A354" s="4">
         <v>36647</v>
       </c>
       <c r="B354" s="4">
@@ -6500,8 +6491,8 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A355" s="9">
+    <row r="355" spans="1:6">
+      <c r="A355" s="4">
         <v>36678</v>
       </c>
       <c r="B355" s="4">
@@ -6517,8 +6508,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A356" s="9">
+    <row r="356" spans="1:6">
+      <c r="A356" s="4">
         <v>36708</v>
       </c>
       <c r="B356" s="4">
@@ -6534,8 +6525,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A357" s="9">
+    <row r="357" spans="1:6">
+      <c r="A357" s="4">
         <v>36739</v>
       </c>
       <c r="B357" s="4">
@@ -6551,8 +6542,8 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A358" s="9">
+    <row r="358" spans="1:6">
+      <c r="A358" s="4">
         <v>36770</v>
       </c>
       <c r="B358" s="4">
@@ -6568,8 +6559,8 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A359" s="9">
+    <row r="359" spans="1:6">
+      <c r="A359" s="4">
         <v>36800</v>
       </c>
       <c r="B359" s="4">
@@ -6585,8 +6576,8 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A360" s="9">
+    <row r="360" spans="1:6">
+      <c r="A360" s="4">
         <v>36831</v>
       </c>
       <c r="B360" s="4">
@@ -6602,8 +6593,8 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A361" s="9">
+    <row r="361" spans="1:6">
+      <c r="A361" s="4">
         <v>36861</v>
       </c>
       <c r="B361" s="4">
@@ -6619,8 +6610,8 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A362" s="9">
+    <row r="362" spans="1:6">
+      <c r="A362" s="4">
         <v>36892</v>
       </c>
       <c r="B362" s="4">
@@ -6636,8 +6627,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A363" s="9">
+    <row r="363" spans="1:6">
+      <c r="A363" s="4">
         <v>36923</v>
       </c>
       <c r="B363" s="4">
@@ -6653,8 +6644,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A364" s="9">
+    <row r="364" spans="1:6">
+      <c r="A364" s="4">
         <v>36951</v>
       </c>
       <c r="B364" s="4">
@@ -6670,8 +6661,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A365" s="9">
+    <row r="365" spans="1:6">
+      <c r="A365" s="4">
         <v>36982</v>
       </c>
       <c r="B365" s="4">
@@ -6687,8 +6678,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A366" s="9">
+    <row r="366" spans="1:6">
+      <c r="A366" s="4">
         <v>37012</v>
       </c>
       <c r="B366" s="4">
@@ -6704,8 +6695,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A367" s="9">
+    <row r="367" spans="1:6">
+      <c r="A367" s="4">
         <v>37043</v>
       </c>
       <c r="B367" s="4">
@@ -6721,8 +6712,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A368" s="9">
+    <row r="368" spans="1:6">
+      <c r="A368" s="4">
         <v>37073</v>
       </c>
       <c r="B368" s="4">
@@ -6738,8 +6729,8 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A369" s="9">
+    <row r="369" spans="1:6">
+      <c r="A369" s="4">
         <v>37104</v>
       </c>
       <c r="B369" s="4">
@@ -6755,8 +6746,8 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A370" s="9">
+    <row r="370" spans="1:6">
+      <c r="A370" s="4">
         <v>37135</v>
       </c>
       <c r="B370" s="4">
@@ -6772,8 +6763,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A371" s="9">
+    <row r="371" spans="1:6">
+      <c r="A371" s="4">
         <v>37165</v>
       </c>
       <c r="B371" s="4">
@@ -6789,8 +6780,8 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A372" s="9">
+    <row r="372" spans="1:6">
+      <c r="A372" s="4">
         <v>37196</v>
       </c>
       <c r="B372" s="4">
@@ -6806,8 +6797,8 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A373" s="9">
+    <row r="373" spans="1:6">
+      <c r="A373" s="4">
         <v>37226</v>
       </c>
       <c r="B373" s="4">
@@ -6823,8 +6814,8 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A374" s="9">
+    <row r="374" spans="1:6">
+      <c r="A374" s="4">
         <v>37257</v>
       </c>
       <c r="B374" s="4">
@@ -6840,8 +6831,8 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A375" s="9">
+    <row r="375" spans="1:6">
+      <c r="A375" s="4">
         <v>37288</v>
       </c>
       <c r="B375" s="4">
@@ -6857,8 +6848,8 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A376" s="9">
+    <row r="376" spans="1:6">
+      <c r="A376" s="4">
         <v>37316</v>
       </c>
       <c r="B376" s="4">
@@ -6874,8 +6865,8 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A377" s="9">
+    <row r="377" spans="1:6">
+      <c r="A377" s="4">
         <v>37347</v>
       </c>
       <c r="B377" s="4">
@@ -6891,8 +6882,8 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A378" s="9">
+    <row r="378" spans="1:6">
+      <c r="A378" s="4">
         <v>37377</v>
       </c>
       <c r="B378" s="4">
@@ -6908,8 +6899,8 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A379" s="9">
+    <row r="379" spans="1:6">
+      <c r="A379" s="4">
         <v>37408</v>
       </c>
       <c r="B379" s="4">
@@ -6925,8 +6916,8 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A380" s="9">
+    <row r="380" spans="1:6">
+      <c r="A380" s="4">
         <v>37438</v>
       </c>
       <c r="B380" s="4">
@@ -6942,8 +6933,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A381" s="9">
+    <row r="381" spans="1:6">
+      <c r="A381" s="4">
         <v>37469</v>
       </c>
       <c r="B381" s="4">
@@ -6959,8 +6950,8 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A382" s="9">
+    <row r="382" spans="1:6">
+      <c r="A382" s="4">
         <v>37500</v>
       </c>
       <c r="B382" s="4">
@@ -6976,8 +6967,8 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A383" s="9">
+    <row r="383" spans="1:6">
+      <c r="A383" s="4">
         <v>37530</v>
       </c>
       <c r="B383" s="4">
@@ -6993,8 +6984,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A384" s="9">
+    <row r="384" spans="1:6">
+      <c r="A384" s="4">
         <v>37561</v>
       </c>
       <c r="B384" s="4">
@@ -7010,8 +7001,8 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A385" s="9">
+    <row r="385" spans="1:6">
+      <c r="A385" s="4">
         <v>37591</v>
       </c>
       <c r="B385" s="4">
@@ -7027,8 +7018,8 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A386" s="9">
+    <row r="386" spans="1:6">
+      <c r="A386" s="4">
         <v>37622</v>
       </c>
       <c r="B386" s="4">
@@ -7044,8 +7035,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A387" s="9">
+    <row r="387" spans="1:6">
+      <c r="A387" s="4">
         <v>37653</v>
       </c>
       <c r="B387" s="4">
@@ -7061,8 +7052,8 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A388" s="9">
+    <row r="388" spans="1:6">
+      <c r="A388" s="4">
         <v>37681</v>
       </c>
       <c r="B388" s="4">
@@ -7078,8 +7069,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A389" s="9">
+    <row r="389" spans="1:6">
+      <c r="A389" s="4">
         <v>37712</v>
       </c>
       <c r="B389" s="4">
@@ -7095,8 +7086,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A390" s="9">
+    <row r="390" spans="1:6">
+      <c r="A390" s="4">
         <v>37742</v>
       </c>
       <c r="B390" s="4">
@@ -7112,8 +7103,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A391" s="9">
+    <row r="391" spans="1:6">
+      <c r="A391" s="4">
         <v>37773</v>
       </c>
       <c r="B391" s="4">
@@ -7129,8 +7120,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A392" s="9">
+    <row r="392" spans="1:6">
+      <c r="A392" s="4">
         <v>37803</v>
       </c>
       <c r="B392" s="4">
@@ -7146,8 +7137,8 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A393" s="9">
+    <row r="393" spans="1:6">
+      <c r="A393" s="4">
         <v>37834</v>
       </c>
       <c r="B393" s="4">
@@ -7163,8 +7154,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A394" s="9">
+    <row r="394" spans="1:6">
+      <c r="A394" s="4">
         <v>37865</v>
       </c>
       <c r="B394" s="4">
@@ -7180,8 +7171,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A395" s="9">
+    <row r="395" spans="1:6">
+      <c r="A395" s="4">
         <v>37895</v>
       </c>
       <c r="B395" s="4">
@@ -7197,8 +7188,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A396" s="9">
+    <row r="396" spans="1:6">
+      <c r="A396" s="4">
         <v>37926</v>
       </c>
       <c r="B396" s="4">
@@ -7214,8 +7205,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A397" s="9">
+    <row r="397" spans="1:6">
+      <c r="A397" s="4">
         <v>37956</v>
       </c>
       <c r="B397" s="4">
@@ -7231,8 +7222,8 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A398" s="9">
+    <row r="398" spans="1:6">
+      <c r="A398" s="4">
         <v>37987</v>
       </c>
       <c r="B398" s="4">
@@ -7248,8 +7239,8 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A399" s="9">
+    <row r="399" spans="1:6">
+      <c r="A399" s="4">
         <v>38018</v>
       </c>
       <c r="B399" s="4">
@@ -7265,8 +7256,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A400" s="9">
+    <row r="400" spans="1:6">
+      <c r="A400" s="4">
         <v>38047</v>
       </c>
       <c r="B400" s="4">
@@ -7282,8 +7273,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A401" s="9">
+    <row r="401" spans="1:6">
+      <c r="A401" s="4">
         <v>38078</v>
       </c>
       <c r="B401" s="4">
@@ -7299,8 +7290,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A402" s="9">
+    <row r="402" spans="1:6">
+      <c r="A402" s="4">
         <v>38108</v>
       </c>
       <c r="B402" s="4">
@@ -7316,8 +7307,8 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A403" s="9">
+    <row r="403" spans="1:6">
+      <c r="A403" s="4">
         <v>38139</v>
       </c>
       <c r="B403" s="4">
@@ -7333,8 +7324,8 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A404" s="9">
+    <row r="404" spans="1:6">
+      <c r="A404" s="4">
         <v>38169</v>
       </c>
       <c r="B404" s="4">
@@ -7350,8 +7341,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A405" s="9">
+    <row r="405" spans="1:6">
+      <c r="A405" s="4">
         <v>38200</v>
       </c>
       <c r="B405" s="4">
@@ -7367,8 +7358,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A406" s="9">
+    <row r="406" spans="1:6">
+      <c r="A406" s="4">
         <v>38231</v>
       </c>
       <c r="B406" s="4">
@@ -7384,8 +7375,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A407" s="9">
+    <row r="407" spans="1:6">
+      <c r="A407" s="4">
         <v>38261</v>
       </c>
       <c r="B407" s="4">
@@ -7401,8 +7392,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A408" s="9">
+    <row r="408" spans="1:6">
+      <c r="A408" s="4">
         <v>38292</v>
       </c>
       <c r="B408" s="4">
@@ -7418,8 +7409,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A409" s="9">
+    <row r="409" spans="1:6">
+      <c r="A409" s="4">
         <v>38322</v>
       </c>
       <c r="B409" s="4">
@@ -7435,8 +7426,8 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A410" s="9">
+    <row r="410" spans="1:6">
+      <c r="A410" s="4">
         <v>38353</v>
       </c>
       <c r="B410" s="4">
@@ -7452,8 +7443,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A411" s="9">
+    <row r="411" spans="1:6">
+      <c r="A411" s="4">
         <v>38384</v>
       </c>
       <c r="B411" s="4">
@@ -7469,8 +7460,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A412" s="9">
+    <row r="412" spans="1:6">
+      <c r="A412" s="4">
         <v>38412</v>
       </c>
       <c r="B412" s="4">
@@ -7486,8 +7477,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A413" s="9">
+    <row r="413" spans="1:6">
+      <c r="A413" s="4">
         <v>38443</v>
       </c>
       <c r="B413" s="4">
@@ -7503,8 +7494,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A414" s="9">
+    <row r="414" spans="1:6">
+      <c r="A414" s="4">
         <v>38473</v>
       </c>
       <c r="B414" s="4">
@@ -7520,8 +7511,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A415" s="9">
+    <row r="415" spans="1:6">
+      <c r="A415" s="4">
         <v>38504</v>
       </c>
       <c r="B415" s="4">
@@ -7537,8 +7528,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A416" s="9">
+    <row r="416" spans="1:6">
+      <c r="A416" s="4">
         <v>38534</v>
       </c>
       <c r="B416" s="4">
@@ -7554,8 +7545,8 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A417" s="9">
+    <row r="417" spans="1:6">
+      <c r="A417" s="4">
         <v>38565</v>
       </c>
       <c r="B417" s="4">
@@ -7571,8 +7562,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A418" s="9">
+    <row r="418" spans="1:6">
+      <c r="A418" s="4">
         <v>38596</v>
       </c>
       <c r="B418" s="4">
@@ -7588,8 +7579,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A419" s="9">
+    <row r="419" spans="1:6">
+      <c r="A419" s="4">
         <v>38626</v>
       </c>
       <c r="B419" s="4">
@@ -7605,8 +7596,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A420" s="9">
+    <row r="420" spans="1:6">
+      <c r="A420" s="4">
         <v>38657</v>
       </c>
       <c r="B420" s="4">
@@ -7622,8 +7613,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A421" s="9">
+    <row r="421" spans="1:6">
+      <c r="A421" s="4">
         <v>38687</v>
       </c>
       <c r="B421" s="4">
@@ -7639,8 +7630,8 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A422" s="9">
+    <row r="422" spans="1:6">
+      <c r="A422" s="4">
         <v>38718</v>
       </c>
       <c r="B422" s="4">
@@ -7656,8 +7647,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A423" s="9">
+    <row r="423" spans="1:6">
+      <c r="A423" s="4">
         <v>38749</v>
       </c>
       <c r="B423" s="4">
@@ -7673,8 +7664,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A424" s="9">
+    <row r="424" spans="1:6">
+      <c r="A424" s="4">
         <v>38777</v>
       </c>
       <c r="B424" s="4">
@@ -7690,8 +7681,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A425" s="9">
+    <row r="425" spans="1:6">
+      <c r="A425" s="4">
         <v>38808</v>
       </c>
       <c r="B425" s="4">
@@ -7707,8 +7698,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A426" s="9">
+    <row r="426" spans="1:6">
+      <c r="A426" s="4">
         <v>38838</v>
       </c>
       <c r="B426" s="4">
@@ -7724,8 +7715,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A427" s="9">
+    <row r="427" spans="1:6">
+      <c r="A427" s="4">
         <v>38869</v>
       </c>
       <c r="B427" s="4">
@@ -7741,8 +7732,8 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A428" s="9">
+    <row r="428" spans="1:6">
+      <c r="A428" s="4">
         <v>38899</v>
       </c>
       <c r="B428" s="4">
@@ -7758,8 +7749,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A429" s="9">
+    <row r="429" spans="1:6">
+      <c r="A429" s="4">
         <v>38930</v>
       </c>
       <c r="B429" s="4">
@@ -7775,8 +7766,8 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A430" s="9">
+    <row r="430" spans="1:6">
+      <c r="A430" s="4">
         <v>38961</v>
       </c>
       <c r="B430" s="4">
@@ -7792,8 +7783,8 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A431" s="9">
+    <row r="431" spans="1:6">
+      <c r="A431" s="4">
         <v>38991</v>
       </c>
       <c r="B431" s="4">
@@ -7809,8 +7800,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A432" s="9">
+    <row r="432" spans="1:6">
+      <c r="A432" s="4">
         <v>39022</v>
       </c>
       <c r="B432" s="4">
@@ -7826,8 +7817,8 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A433" s="9">
+    <row r="433" spans="1:6">
+      <c r="A433" s="4">
         <v>39052</v>
       </c>
       <c r="B433" s="4">
@@ -7843,8 +7834,8 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A434" s="9">
+    <row r="434" spans="1:6">
+      <c r="A434" s="4">
         <v>39083</v>
       </c>
       <c r="B434" s="4">
@@ -7860,8 +7851,8 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A435" s="9">
+    <row r="435" spans="1:6">
+      <c r="A435" s="4">
         <v>39114</v>
       </c>
       <c r="B435" s="4">
@@ -7877,8 +7868,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A436" s="9">
+    <row r="436" spans="1:6">
+      <c r="A436" s="4">
         <v>39142</v>
       </c>
       <c r="B436" s="4">
@@ -7894,8 +7885,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A437" s="9">
+    <row r="437" spans="1:6">
+      <c r="A437" s="4">
         <v>39173</v>
       </c>
       <c r="B437" s="4">
@@ -7911,8 +7902,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A438" s="9">
+    <row r="438" spans="1:6">
+      <c r="A438" s="4">
         <v>39203</v>
       </c>
       <c r="B438" s="4">
@@ -7928,8 +7919,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A439" s="9">
+    <row r="439" spans="1:6">
+      <c r="A439" s="4">
         <v>39234</v>
       </c>
       <c r="B439" s="4">
@@ -7945,8 +7936,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A440" s="9">
+    <row r="440" spans="1:6">
+      <c r="A440" s="4">
         <v>39264</v>
       </c>
       <c r="B440" s="4">
@@ -7962,8 +7953,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A441" s="9">
+    <row r="441" spans="1:6">
+      <c r="A441" s="4">
         <v>39295</v>
       </c>
       <c r="B441" s="4">
@@ -7979,8 +7970,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A442" s="9">
+    <row r="442" spans="1:6">
+      <c r="A442" s="4">
         <v>39326</v>
       </c>
       <c r="B442" s="4">
@@ -7996,8 +7987,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A443" s="9">
+    <row r="443" spans="1:6">
+      <c r="A443" s="4">
         <v>39356</v>
       </c>
       <c r="B443" s="4">
@@ -8013,8 +8004,8 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A444" s="9">
+    <row r="444" spans="1:6">
+      <c r="A444" s="4">
         <v>39387</v>
       </c>
       <c r="B444" s="4">
@@ -8030,8 +8021,8 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A445" s="9">
+    <row r="445" spans="1:6">
+      <c r="A445" s="4">
         <v>39417</v>
       </c>
       <c r="B445" s="4">
@@ -8047,8 +8038,8 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A446" s="9">
+    <row r="446" spans="1:6">
+      <c r="A446" s="4">
         <v>39448</v>
       </c>
       <c r="B446" s="4">
@@ -8064,8 +8055,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A447" s="9">
+    <row r="447" spans="1:6">
+      <c r="A447" s="4">
         <v>39479</v>
       </c>
       <c r="B447" s="4">
@@ -8081,8 +8072,8 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A448" s="9">
+    <row r="448" spans="1:6">
+      <c r="A448" s="4">
         <v>39508</v>
       </c>
       <c r="B448" s="4">
@@ -8098,8 +8089,8 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A449" s="9">
+    <row r="449" spans="1:6">
+      <c r="A449" s="4">
         <v>39539</v>
       </c>
       <c r="B449" s="4">
@@ -8115,8 +8106,8 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A450" s="9">
+    <row r="450" spans="1:6">
+      <c r="A450" s="4">
         <v>39569</v>
       </c>
       <c r="B450" s="4">
@@ -8132,8 +8123,8 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A451" s="9">
+    <row r="451" spans="1:6">
+      <c r="A451" s="4">
         <v>39600</v>
       </c>
       <c r="B451" s="4">
@@ -8149,8 +8140,8 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A452" s="9">
+    <row r="452" spans="1:6">
+      <c r="A452" s="4">
         <v>39630</v>
       </c>
       <c r="B452" s="4">
@@ -8166,8 +8157,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A453" s="9">
+    <row r="453" spans="1:6">
+      <c r="A453" s="4">
         <v>39661</v>
       </c>
       <c r="B453" s="4">
@@ -8183,8 +8174,8 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A454" s="9">
+    <row r="454" spans="1:6">
+      <c r="A454" s="4">
         <v>39692</v>
       </c>
       <c r="B454" s="4">
@@ -8200,8 +8191,8 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A455" s="9">
+    <row r="455" spans="1:6">
+      <c r="A455" s="4">
         <v>39722</v>
       </c>
       <c r="B455" s="4">
@@ -8217,8 +8208,8 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A456" s="9">
+    <row r="456" spans="1:6">
+      <c r="A456" s="4">
         <v>39753</v>
       </c>
       <c r="B456" s="4">
@@ -8234,8 +8225,8 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A457" s="9">
+    <row r="457" spans="1:6">
+      <c r="A457" s="4">
         <v>39783</v>
       </c>
       <c r="B457" s="4">
@@ -8251,8 +8242,8 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A458" s="9">
+    <row r="458" spans="1:6">
+      <c r="A458" s="4">
         <v>39814</v>
       </c>
       <c r="B458" s="4">
@@ -8268,8 +8259,8 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A459" s="9">
+    <row r="459" spans="1:6">
+      <c r="A459" s="4">
         <v>39845</v>
       </c>
       <c r="B459" s="4">
@@ -8285,8 +8276,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A460" s="9">
+    <row r="460" spans="1:6">
+      <c r="A460" s="4">
         <v>39873</v>
       </c>
       <c r="B460" s="4">
@@ -8302,8 +8293,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A461" s="9">
+    <row r="461" spans="1:6">
+      <c r="A461" s="4">
         <v>39904</v>
       </c>
       <c r="B461" s="4">
@@ -8319,8 +8310,8 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A462" s="9">
+    <row r="462" spans="1:6">
+      <c r="A462" s="4">
         <v>39934</v>
       </c>
       <c r="B462" s="4">
@@ -8336,8 +8327,8 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A463" s="9">
+    <row r="463" spans="1:6">
+      <c r="A463" s="4">
         <v>39965</v>
       </c>
       <c r="B463" s="4">
@@ -8353,8 +8344,8 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A464" s="9">
+    <row r="464" spans="1:6">
+      <c r="A464" s="4">
         <v>39995</v>
       </c>
       <c r="B464" s="4">
@@ -8370,8 +8361,8 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A465" s="9">
+    <row r="465" spans="1:6">
+      <c r="A465" s="4">
         <v>40026</v>
       </c>
       <c r="B465" s="4">
@@ -8387,8 +8378,8 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A466" s="9">
+    <row r="466" spans="1:6">
+      <c r="A466" s="4">
         <v>40057</v>
       </c>
       <c r="B466" s="4">
@@ -8404,8 +8395,8 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A467" s="9">
+    <row r="467" spans="1:6">
+      <c r="A467" s="4">
         <v>40087</v>
       </c>
       <c r="B467" s="4">
@@ -8421,8 +8412,8 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A468" s="9">
+    <row r="468" spans="1:6">
+      <c r="A468" s="4">
         <v>40118</v>
       </c>
       <c r="B468" s="4">
@@ -8438,8 +8429,8 @@
         <v>-2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A469" s="9">
+    <row r="469" spans="1:6">
+      <c r="A469" s="4">
         <v>40148</v>
       </c>
       <c r="B469" s="4">
@@ -8455,8 +8446,8 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A470" s="9">
+    <row r="470" spans="1:6">
+      <c r="A470" s="4">
         <v>40179</v>
       </c>
       <c r="B470" s="4">
@@ -8472,8 +8463,8 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A471" s="9">
+    <row r="471" spans="1:6">
+      <c r="A471" s="4">
         <v>40210</v>
       </c>
       <c r="B471" s="4">
@@ -8489,8 +8480,8 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A472" s="9">
+    <row r="472" spans="1:6">
+      <c r="A472" s="4">
         <v>40238</v>
       </c>
       <c r="B472" s="4">
@@ -8506,8 +8497,8 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A473" s="9">
+    <row r="473" spans="1:6">
+      <c r="A473" s="4">
         <v>40269</v>
       </c>
       <c r="B473" s="4">
@@ -8523,8 +8514,8 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A474" s="9">
+    <row r="474" spans="1:6">
+      <c r="A474" s="4">
         <v>40299</v>
       </c>
       <c r="B474" s="4">
@@ -8540,8 +8531,8 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A475" s="9">
+    <row r="475" spans="1:6">
+      <c r="A475" s="4">
         <v>40330</v>
       </c>
       <c r="B475" s="4">
@@ -8557,8 +8548,8 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A476" s="9">
+    <row r="476" spans="1:6">
+      <c r="A476" s="4">
         <v>40360</v>
       </c>
       <c r="B476" s="4">
@@ -8574,8 +8565,8 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A477" s="9">
+    <row r="477" spans="1:6">
+      <c r="A477" s="4">
         <v>40391</v>
       </c>
       <c r="B477" s="4">
@@ -8591,8 +8582,8 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A478" s="9">
+    <row r="478" spans="1:6">
+      <c r="A478" s="4">
         <v>40422</v>
       </c>
       <c r="B478" s="4">
@@ -8608,8 +8599,8 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A479" s="9">
+    <row r="479" spans="1:6">
+      <c r="A479" s="4">
         <v>40452</v>
       </c>
       <c r="B479" s="4">
@@ -8625,8 +8616,8 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A480" s="9">
+    <row r="480" spans="1:6">
+      <c r="A480" s="4">
         <v>40483</v>
       </c>
       <c r="B480" s="4">
@@ -8642,8 +8633,8 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A481" s="9">
+    <row r="481" spans="1:7">
+      <c r="A481" s="4">
         <v>40513</v>
       </c>
       <c r="B481" s="4">
@@ -8660,8 +8651,8 @@
       </c>
       <c r="G481" s="3"/>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A482" s="9">
+    <row r="482" spans="1:7">
+      <c r="A482" s="4">
         <v>40544</v>
       </c>
       <c r="B482" s="4">
@@ -8678,8 +8669,8 @@
       </c>
       <c r="G482" s="3"/>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A483" s="9">
+    <row r="483" spans="1:7">
+      <c r="A483" s="4">
         <v>40575</v>
       </c>
       <c r="B483" s="4">
@@ -8696,8 +8687,8 @@
       </c>
       <c r="G483" s="3"/>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A484" s="9">
+    <row r="484" spans="1:7">
+      <c r="A484" s="4">
         <v>40603</v>
       </c>
       <c r="B484" s="4">
@@ -8714,8 +8705,8 @@
       </c>
       <c r="G484" s="3"/>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A485" s="9">
+    <row r="485" spans="1:7">
+      <c r="A485" s="4">
         <v>40634</v>
       </c>
       <c r="B485" s="4">
@@ -8732,8 +8723,8 @@
       </c>
       <c r="G485" s="3"/>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A486" s="9">
+    <row r="486" spans="1:7">
+      <c r="A486" s="4">
         <v>40664</v>
       </c>
       <c r="B486" s="4">
@@ -8750,8 +8741,8 @@
       </c>
       <c r="G486" s="3"/>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A487" s="9">
+    <row r="487" spans="1:7">
+      <c r="A487" s="4">
         <v>40695</v>
       </c>
       <c r="B487" s="4">
@@ -8768,8 +8759,8 @@
       </c>
       <c r="G487" s="3"/>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A488" s="9">
+    <row r="488" spans="1:7">
+      <c r="A488" s="4">
         <v>40725</v>
       </c>
       <c r="B488" s="4">
@@ -8786,8 +8777,8 @@
       </c>
       <c r="G488" s="3"/>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A489" s="9">
+    <row r="489" spans="1:7">
+      <c r="A489" s="4">
         <v>40756</v>
       </c>
       <c r="B489" s="4">
@@ -8804,8 +8795,8 @@
       </c>
       <c r="G489" s="3"/>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A490" s="9">
+    <row r="490" spans="1:7">
+      <c r="A490" s="4">
         <v>40787</v>
       </c>
       <c r="B490" s="4">
@@ -8822,8 +8813,8 @@
       </c>
       <c r="G490" s="3"/>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A491" s="9">
+    <row r="491" spans="1:7">
+      <c r="A491" s="4">
         <v>40817</v>
       </c>
       <c r="B491" s="4">
@@ -8840,8 +8831,8 @@
       </c>
       <c r="G491" s="3"/>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A492" s="9">
+    <row r="492" spans="1:7">
+      <c r="A492" s="4">
         <v>40848</v>
       </c>
       <c r="B492" s="4">
@@ -8858,8 +8849,8 @@
       </c>
       <c r="G492" s="3"/>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A493" s="9">
+    <row r="493" spans="1:7">
+      <c r="A493" s="4">
         <v>40878</v>
       </c>
       <c r="B493" s="4">
@@ -8876,8 +8867,8 @@
       </c>
       <c r="G493" s="3"/>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A494" s="9">
+    <row r="494" spans="1:7">
+      <c r="A494" s="4">
         <v>40909</v>
       </c>
       <c r="B494" s="4">
@@ -8894,8 +8885,8 @@
       </c>
       <c r="G494" s="3"/>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A495" s="9">
+    <row r="495" spans="1:7">
+      <c r="A495" s="4">
         <v>40940</v>
       </c>
       <c r="B495" s="4">
@@ -8912,8 +8903,8 @@
       </c>
       <c r="G495" s="3"/>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A496" s="9">
+    <row r="496" spans="1:7">
+      <c r="A496" s="4">
         <v>40969</v>
       </c>
       <c r="B496" s="4">
@@ -8930,8 +8921,8 @@
       </c>
       <c r="G496" s="3"/>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A497" s="9">
+    <row r="497" spans="1:7">
+      <c r="A497" s="4">
         <v>41000</v>
       </c>
       <c r="B497" s="4">
@@ -8948,8 +8939,8 @@
       </c>
       <c r="G497" s="3"/>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A498" s="9">
+    <row r="498" spans="1:7">
+      <c r="A498" s="4">
         <v>41030</v>
       </c>
       <c r="B498" s="4">
@@ -8966,8 +8957,8 @@
       </c>
       <c r="G498" s="3"/>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A499" s="9">
+    <row r="499" spans="1:7">
+      <c r="A499" s="4">
         <v>41061</v>
       </c>
       <c r="B499" s="4">
@@ -8984,8 +8975,8 @@
       </c>
       <c r="G499" s="3"/>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A500" s="9">
+    <row r="500" spans="1:7">
+      <c r="A500" s="4">
         <v>41091</v>
       </c>
       <c r="B500" s="4">
@@ -9002,8 +8993,8 @@
       </c>
       <c r="G500" s="3"/>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A501" s="9">
+    <row r="501" spans="1:7">
+      <c r="A501" s="4">
         <v>41122</v>
       </c>
       <c r="B501" s="4">
@@ -9020,8 +9011,8 @@
       </c>
       <c r="G501" s="3"/>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A502" s="9">
+    <row r="502" spans="1:7">
+      <c r="A502" s="4">
         <v>41153</v>
       </c>
       <c r="B502" s="4">
@@ -9038,8 +9029,8 @@
       </c>
       <c r="G502" s="3"/>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A503" s="9">
+    <row r="503" spans="1:7">
+      <c r="A503" s="4">
         <v>41183</v>
       </c>
       <c r="B503" s="4">
@@ -9056,8 +9047,8 @@
       </c>
       <c r="G503" s="3"/>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A504" s="9">
+    <row r="504" spans="1:7">
+      <c r="A504" s="4">
         <v>41214</v>
       </c>
       <c r="B504" s="4">
@@ -9074,8 +9065,8 @@
       </c>
       <c r="G504" s="3"/>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A505" s="9">
+    <row r="505" spans="1:7">
+      <c r="A505" s="4">
         <v>41244</v>
       </c>
       <c r="B505" s="4">
@@ -9092,8 +9083,8 @@
       </c>
       <c r="G505" s="3"/>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A506" s="9">
+    <row r="506" spans="1:7">
+      <c r="A506" s="4">
         <v>41275</v>
       </c>
       <c r="B506" s="4">
@@ -9110,8 +9101,8 @@
       </c>
       <c r="G506" s="3"/>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A507" s="9">
+    <row r="507" spans="1:7">
+      <c r="A507" s="4">
         <v>41306</v>
       </c>
       <c r="B507" s="4">
@@ -9128,8 +9119,8 @@
       </c>
       <c r="G507" s="3"/>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A508" s="9">
+    <row r="508" spans="1:7">
+      <c r="A508" s="4">
         <v>41334</v>
       </c>
       <c r="B508" s="4">
@@ -9146,8 +9137,8 @@
       </c>
       <c r="G508" s="3"/>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A509" s="9">
+    <row r="509" spans="1:7">
+      <c r="A509" s="4">
         <v>41365</v>
       </c>
       <c r="B509" s="4">
@@ -9164,8 +9155,8 @@
       </c>
       <c r="G509" s="3"/>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A510" s="9">
+    <row r="510" spans="1:7">
+      <c r="A510" s="4">
         <v>41395</v>
       </c>
       <c r="B510" s="4">
@@ -9185,8 +9176,8 @@
       </c>
       <c r="G510" s="3"/>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A511" s="9">
+    <row r="511" spans="1:7">
+      <c r="A511" s="4">
         <v>41426</v>
       </c>
       <c r="B511" s="4">
@@ -9206,8 +9197,8 @@
       </c>
       <c r="G511" s="3"/>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A512" s="9">
+    <row r="512" spans="1:7">
+      <c r="A512" s="4">
         <v>41456</v>
       </c>
       <c r="B512" s="4">
@@ -9224,8 +9215,8 @@
       </c>
       <c r="G512" s="3"/>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A513" s="9">
+    <row r="513" spans="1:7">
+      <c r="A513" s="4">
         <v>41487</v>
       </c>
       <c r="B513" s="4">
@@ -9245,8 +9236,8 @@
       </c>
       <c r="G513" s="3"/>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A514" s="9">
+    <row r="514" spans="1:7">
+      <c r="A514" s="4">
         <v>41518</v>
       </c>
       <c r="B514" s="4">
@@ -9266,8 +9257,8 @@
       </c>
       <c r="G514" s="3"/>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A515" s="9">
+    <row r="515" spans="1:7">
+      <c r="A515" s="4">
         <v>41548</v>
       </c>
       <c r="B515" s="4">
@@ -9287,8 +9278,8 @@
       </c>
       <c r="G515" s="3"/>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A516" s="9">
+    <row r="516" spans="1:7">
+      <c r="A516" s="4">
         <v>41579</v>
       </c>
       <c r="B516" s="4">
@@ -9305,8 +9296,8 @@
       </c>
       <c r="G516" s="3"/>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A517" s="9">
+    <row r="517" spans="1:7">
+      <c r="A517" s="4">
         <v>41609</v>
       </c>
       <c r="B517" s="4">
@@ -9323,8 +9314,8 @@
       </c>
       <c r="G517" s="3"/>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A518" s="9">
+    <row r="518" spans="1:7">
+      <c r="A518" s="4">
         <v>41640</v>
       </c>
       <c r="B518" s="4">
@@ -9341,8 +9332,8 @@
       </c>
       <c r="G518" s="3"/>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A519" s="9">
+    <row r="519" spans="1:7">
+      <c r="A519" s="4">
         <v>41671</v>
       </c>
       <c r="B519" s="4">
@@ -9362,8 +9353,8 @@
       </c>
       <c r="G519" s="3"/>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A520" s="9">
+    <row r="520" spans="1:7">
+      <c r="A520" s="4">
         <v>41699</v>
       </c>
       <c r="B520" s="4">
@@ -9380,8 +9371,8 @@
       </c>
       <c r="G520" s="3"/>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A521" s="9">
+    <row r="521" spans="1:7">
+      <c r="A521" s="4">
         <v>41730</v>
       </c>
       <c r="B521" s="4">
@@ -9398,8 +9389,8 @@
       </c>
       <c r="G521" s="3"/>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A522" s="9">
+    <row r="522" spans="1:7">
+      <c r="A522" s="4">
         <v>41760</v>
       </c>
       <c r="B522" s="4">
@@ -9416,8 +9407,8 @@
       </c>
       <c r="G522" s="3"/>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A523" s="9">
+    <row r="523" spans="1:7">
+      <c r="A523" s="4">
         <v>41791</v>
       </c>
       <c r="B523" s="4">
@@ -9434,8 +9425,8 @@
       </c>
       <c r="G523" s="3"/>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A524" s="9">
+    <row r="524" spans="1:7">
+      <c r="A524" s="4">
         <v>41821</v>
       </c>
       <c r="B524" s="4">
@@ -9452,8 +9443,8 @@
       </c>
       <c r="G524" s="3"/>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A525" s="9">
+    <row r="525" spans="1:7">
+      <c r="A525" s="4">
         <v>41852</v>
       </c>
       <c r="B525" s="4">
@@ -9473,8 +9464,8 @@
       </c>
       <c r="G525" s="3"/>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A526" s="9">
+    <row r="526" spans="1:7">
+      <c r="A526" s="4">
         <v>41883</v>
       </c>
       <c r="B526" s="4">
@@ -9494,8 +9485,8 @@
       </c>
       <c r="G526" s="3"/>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A527" s="9">
+    <row r="527" spans="1:7">
+      <c r="A527" s="4">
         <v>41913</v>
       </c>
       <c r="B527" s="4">
@@ -9515,8 +9506,8 @@
       </c>
       <c r="G527" s="3"/>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A528" s="9">
+    <row r="528" spans="1:7">
+      <c r="A528" s="4">
         <v>41944</v>
       </c>
       <c r="B528" s="4">
@@ -9533,8 +9524,8 @@
       </c>
       <c r="G528" s="3"/>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A529" s="9">
+    <row r="529" spans="1:7">
+      <c r="A529" s="4">
         <v>41974</v>
       </c>
       <c r="B529" s="4">
@@ -9554,8 +9545,8 @@
       </c>
       <c r="G529" s="3"/>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A530" s="9">
+    <row r="530" spans="1:7">
+      <c r="A530" s="4">
         <v>42005</v>
       </c>
       <c r="B530" s="4">
@@ -9575,8 +9566,8 @@
       </c>
       <c r="G530" s="3"/>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A531" s="9">
+    <row r="531" spans="1:7">
+      <c r="A531" s="4">
         <v>42036</v>
       </c>
       <c r="B531" s="4">
@@ -9593,8 +9584,8 @@
       </c>
       <c r="G531" s="3"/>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A532" s="9">
+    <row r="532" spans="1:7">
+      <c r="A532" s="4">
         <v>42064</v>
       </c>
       <c r="B532" s="4">
@@ -9611,8 +9602,8 @@
       </c>
       <c r="G532" s="3"/>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A533" s="9">
+    <row r="533" spans="1:7">
+      <c r="A533" s="4">
         <v>42095</v>
       </c>
       <c r="B533" s="4">
@@ -9632,8 +9623,8 @@
       </c>
       <c r="G533" s="3"/>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A534" s="9">
+    <row r="534" spans="1:7">
+      <c r="A534" s="4">
         <v>42125</v>
       </c>
       <c r="B534" s="4">
@@ -9653,8 +9644,8 @@
       </c>
       <c r="G534" s="3"/>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A535" s="9">
+    <row r="535" spans="1:7">
+      <c r="A535" s="4">
         <v>42156</v>
       </c>
       <c r="B535" s="4">
@@ -9674,8 +9665,8 @@
       </c>
       <c r="G535" s="3"/>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A536" s="9">
+    <row r="536" spans="1:7">
+      <c r="A536" s="4">
         <v>42186</v>
       </c>
       <c r="B536" s="4">
@@ -9695,8 +9686,8 @@
       </c>
       <c r="G536" s="3"/>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A537" s="9">
+    <row r="537" spans="1:7">
+      <c r="A537" s="4">
         <v>42217</v>
       </c>
       <c r="B537" s="4">
@@ -9716,8 +9707,8 @@
       </c>
       <c r="G537" s="3"/>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A538" s="9">
+    <row r="538" spans="1:7">
+      <c r="A538" s="4">
         <v>42248</v>
       </c>
       <c r="B538" s="4">
@@ -9737,8 +9728,8 @@
       </c>
       <c r="G538" s="3"/>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A539" s="9">
+    <row r="539" spans="1:7">
+      <c r="A539" s="4">
         <v>42278</v>
       </c>
       <c r="B539" s="4">
@@ -9758,8 +9749,8 @@
       </c>
       <c r="G539" s="3"/>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A540" s="9">
+    <row r="540" spans="1:7">
+      <c r="A540" s="4">
         <v>42309</v>
       </c>
       <c r="B540" s="4">
@@ -9779,8 +9770,8 @@
       </c>
       <c r="G540" s="3"/>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A541" s="9">
+    <row r="541" spans="1:7">
+      <c r="A541" s="4">
         <v>42339</v>
       </c>
       <c r="B541" s="4">
@@ -9800,8 +9791,8 @@
       </c>
       <c r="G541" s="3"/>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A542" s="9">
+    <row r="542" spans="1:7">
+      <c r="A542" s="4">
         <v>42370</v>
       </c>
       <c r="B542" s="4">
@@ -9821,8 +9812,8 @@
       </c>
       <c r="G542" s="3"/>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A543" s="9">
+    <row r="543" spans="1:7">
+      <c r="A543" s="4">
         <v>42401</v>
       </c>
       <c r="B543" s="4">
@@ -9842,8 +9833,8 @@
       </c>
       <c r="G543" s="3"/>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A544" s="9">
+    <row r="544" spans="1:7">
+      <c r="A544" s="4">
         <v>42430</v>
       </c>
       <c r="B544" s="4">
@@ -9863,8 +9854,8 @@
       </c>
       <c r="G544" s="3"/>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A545" s="9">
+    <row r="545" spans="1:7">
+      <c r="A545" s="4">
         <v>42461</v>
       </c>
       <c r="B545" s="4">
@@ -9884,8 +9875,8 @@
       </c>
       <c r="G545" s="3"/>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A546" s="9">
+    <row r="546" spans="1:7">
+      <c r="A546" s="4">
         <v>42491</v>
       </c>
       <c r="B546" s="4">
@@ -9902,8 +9893,8 @@
       </c>
       <c r="G546" s="3"/>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A547" s="9">
+    <row r="547" spans="1:7">
+      <c r="A547" s="4">
         <v>42522</v>
       </c>
       <c r="B547" s="4">
@@ -9923,8 +9914,8 @@
       </c>
       <c r="G547" s="3"/>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A548" s="9">
+    <row r="548" spans="1:7">
+      <c r="A548" s="4">
         <v>42552</v>
       </c>
       <c r="B548" s="4">
@@ -9944,8 +9935,8 @@
       </c>
       <c r="G548" s="3"/>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A549" s="9">
+    <row r="549" spans="1:7">
+      <c r="A549" s="4">
         <v>42583</v>
       </c>
       <c r="B549" s="4">
@@ -9965,8 +9956,8 @@
       </c>
       <c r="G549" s="3"/>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A550" s="9">
+    <row r="550" spans="1:7">
+      <c r="A550" s="4">
         <v>42614</v>
       </c>
       <c r="B550" s="4">
@@ -9986,8 +9977,8 @@
       </c>
       <c r="G550" s="3"/>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A551" s="9">
+    <row r="551" spans="1:7">
+      <c r="A551" s="4">
         <v>42644</v>
       </c>
       <c r="B551" s="4">
@@ -10004,8 +9995,8 @@
       </c>
       <c r="G551" s="3"/>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A552" s="9">
+    <row r="552" spans="1:7">
+      <c r="A552" s="4">
         <v>42675</v>
       </c>
       <c r="B552" s="4">
@@ -10022,8 +10013,8 @@
       </c>
       <c r="G552" s="3"/>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A553" s="9">
+    <row r="553" spans="1:7">
+      <c r="A553" s="4">
         <v>42705</v>
       </c>
       <c r="B553" s="4">
@@ -10043,8 +10034,8 @@
       </c>
       <c r="G553" s="3"/>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A554" s="9">
+    <row r="554" spans="1:7">
+      <c r="A554" s="4">
         <v>42736</v>
       </c>
       <c r="B554" s="4">
@@ -10064,8 +10055,8 @@
       </c>
       <c r="G554" s="3"/>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A555" s="9">
+    <row r="555" spans="1:7">
+      <c r="A555" s="4">
         <v>42767</v>
       </c>
       <c r="B555" s="4">
@@ -10085,8 +10076,8 @@
       </c>
       <c r="G555" s="3"/>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A556" s="9">
+    <row r="556" spans="1:7">
+      <c r="A556" s="4">
         <v>42795</v>
       </c>
       <c r="B556" s="4">
@@ -10106,8 +10097,8 @@
       </c>
       <c r="G556" s="3"/>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A557" s="9">
+    <row r="557" spans="1:7">
+      <c r="A557" s="4">
         <v>42826</v>
       </c>
       <c r="B557" s="4">
@@ -10127,8 +10118,8 @@
       </c>
       <c r="G557" s="3"/>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A558" s="9">
+    <row r="558" spans="1:7">
+      <c r="A558" s="4">
         <v>42856</v>
       </c>
       <c r="B558" s="4">
@@ -10148,8 +10139,8 @@
       </c>
       <c r="G558" s="3"/>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A559" s="9">
+    <row r="559" spans="1:7">
+      <c r="A559" s="4">
         <v>42887</v>
       </c>
       <c r="B559" s="4">
@@ -10169,8 +10160,8 @@
       </c>
       <c r="G559" s="3"/>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A560" s="9">
+    <row r="560" spans="1:7">
+      <c r="A560" s="4">
         <v>42917</v>
       </c>
       <c r="B560" s="4">
@@ -10190,8 +10181,8 @@
       </c>
       <c r="G560" s="3"/>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A561" s="9">
+    <row r="561" spans="1:7">
+      <c r="A561" s="4">
         <v>42948</v>
       </c>
       <c r="B561" s="4">
@@ -10211,8 +10202,8 @@
       </c>
       <c r="G561" s="3"/>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A562" s="9">
+    <row r="562" spans="1:7">
+      <c r="A562" s="4">
         <v>42979</v>
       </c>
       <c r="B562" s="4">
@@ -10232,8 +10223,8 @@
       </c>
       <c r="G562" s="3"/>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A563" s="9">
+    <row r="563" spans="1:7">
+      <c r="A563" s="4">
         <v>43009</v>
       </c>
       <c r="B563" s="4">
@@ -10253,8 +10244,8 @@
       </c>
       <c r="G563" s="3"/>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A564" s="9">
+    <row r="564" spans="1:7">
+      <c r="A564" s="4">
         <v>43040</v>
       </c>
       <c r="B564" s="4">
@@ -10274,8 +10265,8 @@
       </c>
       <c r="G564" s="3"/>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A565" s="9">
+    <row r="565" spans="1:7">
+      <c r="A565" s="4">
         <v>43070</v>
       </c>
       <c r="B565" s="4">
@@ -10295,8 +10286,8 @@
       </c>
       <c r="G565" s="3"/>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A566" s="9">
+    <row r="566" spans="1:7">
+      <c r="A566" s="4">
         <v>43101</v>
       </c>
       <c r="B566" s="4">
@@ -10316,8 +10307,8 @@
       </c>
       <c r="G566" s="3"/>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A567" s="9">
+    <row r="567" spans="1:7">
+      <c r="A567" s="4">
         <v>43132</v>
       </c>
       <c r="B567" s="4">
@@ -10337,8 +10328,8 @@
       </c>
       <c r="G567" s="3"/>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A568" s="9">
+    <row r="568" spans="1:7">
+      <c r="A568" s="4">
         <v>43160</v>
       </c>
       <c r="B568" s="4">
@@ -10358,8 +10349,8 @@
       </c>
       <c r="G568" s="3"/>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A569" s="9">
+    <row r="569" spans="1:7">
+      <c r="A569" s="4">
         <v>43191</v>
       </c>
       <c r="B569" s="4">
@@ -10379,8 +10370,8 @@
       </c>
       <c r="G569" s="3"/>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A570" s="9">
+    <row r="570" spans="1:7">
+      <c r="A570" s="4">
         <v>43221</v>
       </c>
       <c r="B570" s="4">
@@ -10400,8 +10391,8 @@
       </c>
       <c r="G570" s="3"/>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A571" s="9">
+    <row r="571" spans="1:7">
+      <c r="A571" s="4">
         <v>43252</v>
       </c>
       <c r="B571" s="4">
@@ -10421,8 +10412,8 @@
       </c>
       <c r="G571" s="3"/>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A572" s="9">
+    <row r="572" spans="1:7">
+      <c r="A572" s="4">
         <v>43282</v>
       </c>
       <c r="B572" s="4">
@@ -10442,8 +10433,8 @@
       </c>
       <c r="G572" s="3"/>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A573" s="9">
+    <row r="573" spans="1:7">
+      <c r="A573" s="4">
         <v>43313</v>
       </c>
       <c r="B573" s="4">
@@ -10460,8 +10451,8 @@
       </c>
       <c r="G573" s="3"/>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A574" s="9">
+    <row r="574" spans="1:7">
+      <c r="A574" s="4">
         <v>43344</v>
       </c>
       <c r="B574" s="4">
@@ -10478,8 +10469,8 @@
       </c>
       <c r="G574" s="3"/>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A575" s="9">
+    <row r="575" spans="1:7">
+      <c r="A575" s="4">
         <v>43374</v>
       </c>
       <c r="B575" s="4">
@@ -10499,8 +10490,8 @@
       </c>
       <c r="G575" s="3"/>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A576" s="9">
+    <row r="576" spans="1:7">
+      <c r="A576" s="4">
         <v>43405</v>
       </c>
       <c r="B576" s="4">
@@ -10520,8 +10511,8 @@
       </c>
       <c r="G576" s="3"/>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A577" s="9">
+    <row r="577" spans="1:7">
+      <c r="A577" s="4">
         <v>43435</v>
       </c>
       <c r="B577" s="4">
@@ -10541,8 +10532,8 @@
       </c>
       <c r="G577" s="3"/>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A578" s="9">
+    <row r="578" spans="1:7">
+      <c r="A578" s="4">
         <v>43466</v>
       </c>
       <c r="B578" s="4">
@@ -10562,8 +10553,8 @@
       </c>
       <c r="G578" s="3"/>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A579" s="9">
+    <row r="579" spans="1:7">
+      <c r="A579" s="4">
         <v>43497</v>
       </c>
       <c r="B579" s="4">
@@ -10583,8 +10574,8 @@
       </c>
       <c r="G579" s="3"/>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A580" s="9">
+    <row r="580" spans="1:7">
+      <c r="A580" s="4">
         <v>43525</v>
       </c>
       <c r="B580" s="4">
@@ -10604,8 +10595,8 @@
       </c>
       <c r="G580" s="3"/>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A581" s="9">
+    <row r="581" spans="1:7">
+      <c r="A581" s="4">
         <v>43556</v>
       </c>
       <c r="B581" s="4">
@@ -10625,8 +10616,8 @@
       </c>
       <c r="G581" s="3"/>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A582" s="9">
+    <row r="582" spans="1:7">
+      <c r="A582" s="4">
         <v>43586</v>
       </c>
       <c r="B582" s="4">
@@ -10646,8 +10637,8 @@
       </c>
       <c r="G582" s="3"/>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A583" s="9">
+    <row r="583" spans="1:7">
+      <c r="A583" s="4">
         <v>43617</v>
       </c>
       <c r="B583" s="4">
@@ -10667,8 +10658,8 @@
       </c>
       <c r="G583" s="3"/>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A584" s="9">
+    <row r="584" spans="1:7">
+      <c r="A584" s="4">
         <v>43647</v>
       </c>
       <c r="B584" s="4">
@@ -10688,8 +10679,8 @@
       </c>
       <c r="G584" s="3"/>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A585" s="9">
+    <row r="585" spans="1:7">
+      <c r="A585" s="4">
         <v>43678</v>
       </c>
       <c r="B585" s="4">
@@ -10709,8 +10700,8 @@
       </c>
       <c r="G585" s="3"/>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A586" s="9">
+    <row r="586" spans="1:7">
+      <c r="A586" s="4">
         <v>43709</v>
       </c>
       <c r="B586" s="4">
@@ -10730,8 +10721,8 @@
       </c>
       <c r="G586" s="3"/>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A587" s="9">
+    <row r="587" spans="1:7">
+      <c r="A587" s="4">
         <v>43739</v>
       </c>
       <c r="B587" s="4">
@@ -10751,8 +10742,8 @@
       </c>
       <c r="G587" s="3"/>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A588" s="9">
+    <row r="588" spans="1:7">
+      <c r="A588" s="4">
         <v>43770</v>
       </c>
       <c r="B588" s="4">
@@ -10769,8 +10760,8 @@
       </c>
       <c r="G588" s="3"/>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A589" s="9">
+    <row r="589" spans="1:7">
+      <c r="A589" s="4">
         <v>43800</v>
       </c>
       <c r="B589" s="4">
@@ -10787,8 +10778,8 @@
       </c>
       <c r="G589" s="3"/>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A590" s="9">
+    <row r="590" spans="1:7">
+      <c r="A590" s="4">
         <v>43831</v>
       </c>
       <c r="B590" s="4">
@@ -10808,8 +10799,8 @@
       </c>
       <c r="G590" s="3"/>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A591" s="9">
+    <row r="591" spans="1:7">
+      <c r="A591" s="4">
         <v>43862</v>
       </c>
       <c r="B591" s="4">
@@ -10829,8 +10820,8 @@
       </c>
       <c r="G591" s="3"/>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A592" s="9">
+    <row r="592" spans="1:7">
+      <c r="A592" s="4">
         <v>43891</v>
       </c>
       <c r="B592" s="4">
@@ -10847,8 +10838,8 @@
       </c>
       <c r="G592" s="3"/>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A593" s="9">
+    <row r="593" spans="1:7">
+      <c r="A593" s="4">
         <v>43922</v>
       </c>
       <c r="B593" s="4">
@@ -10865,8 +10856,8 @@
       </c>
       <c r="G593" s="3"/>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A594" s="9">
+    <row r="594" spans="1:7">
+      <c r="A594" s="4">
         <v>43952</v>
       </c>
       <c r="B594" s="4">
@@ -10883,8 +10874,8 @@
       </c>
       <c r="G594" s="3"/>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A595" s="9">
+    <row r="595" spans="1:7">
+      <c r="A595" s="4">
         <v>43983</v>
       </c>
       <c r="B595" s="4">
@@ -10901,8 +10892,8 @@
       </c>
       <c r="G595" s="3"/>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A596" s="9">
+    <row r="596" spans="1:7">
+      <c r="A596" s="4">
         <v>44013</v>
       </c>
       <c r="B596" s="4">
@@ -10919,8 +10910,8 @@
       </c>
       <c r="G596" s="3"/>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A597" s="9">
+    <row r="597" spans="1:7">
+      <c r="A597" s="4">
         <v>44044</v>
       </c>
       <c r="B597" s="4">
@@ -10937,8 +10928,8 @@
       </c>
       <c r="G597" s="3"/>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A598" s="9">
+    <row r="598" spans="1:7">
+      <c r="A598" s="4">
         <v>44075</v>
       </c>
       <c r="B598" s="4">
@@ -10955,8 +10946,8 @@
       </c>
       <c r="G598" s="3"/>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A599" s="9">
+    <row r="599" spans="1:7">
+      <c r="A599" s="4">
         <v>44105</v>
       </c>
       <c r="B599" s="4">
@@ -10976,8 +10967,8 @@
       </c>
       <c r="G599" s="3"/>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A600" s="9">
+    <row r="600" spans="1:7">
+      <c r="A600" s="4">
         <v>44136</v>
       </c>
       <c r="B600" s="4">
@@ -10994,8 +10985,8 @@
       </c>
       <c r="G600" s="3"/>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A601" s="9">
+    <row r="601" spans="1:7">
+      <c r="A601" s="4">
         <v>44166</v>
       </c>
       <c r="B601" s="4">
@@ -11012,8 +11003,8 @@
       </c>
       <c r="G601" s="3"/>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A602" s="9">
+    <row r="602" spans="1:7">
+      <c r="A602" s="4">
         <v>44197</v>
       </c>
       <c r="B602" s="4">
@@ -11030,8 +11021,8 @@
       </c>
       <c r="G602" s="3"/>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A603" s="9">
+    <row r="603" spans="1:7">
+      <c r="A603" s="4">
         <v>44228</v>
       </c>
       <c r="B603" s="4">
@@ -11048,8 +11039,8 @@
       </c>
       <c r="G603" s="3"/>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A604" s="9">
+    <row r="604" spans="1:7">
+      <c r="A604" s="4">
         <v>44256</v>
       </c>
       <c r="B604" s="4">
@@ -11066,8 +11057,8 @@
       </c>
       <c r="G604" s="3"/>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A605" s="9">
+    <row r="605" spans="1:7">
+      <c r="A605" s="4">
         <v>44287</v>
       </c>
       <c r="B605" s="4">
@@ -11084,8 +11075,8 @@
       </c>
       <c r="G605" s="3"/>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A606" s="9">
+    <row r="606" spans="1:7">
+      <c r="A606" s="4">
         <v>44317</v>
       </c>
       <c r="B606" s="4">
@@ -11102,8 +11093,8 @@
       </c>
       <c r="G606" s="3"/>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A607" s="9">
+    <row r="607" spans="1:7">
+      <c r="A607" s="4">
         <v>44348</v>
       </c>
       <c r="B607" s="4">
@@ -11120,8 +11111,8 @@
       </c>
       <c r="G607" s="3"/>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A608" s="9">
+    <row r="608" spans="1:7">
+      <c r="A608" s="4">
         <v>44378</v>
       </c>
       <c r="B608" s="4">
@@ -11138,8 +11129,8 @@
       </c>
       <c r="G608" s="3"/>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A609" s="9">
+    <row r="609" spans="1:7">
+      <c r="A609" s="4">
         <v>44409</v>
       </c>
       <c r="B609" s="4">
@@ -11156,8 +11147,8 @@
       </c>
       <c r="G609" s="3"/>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A610" s="9">
+    <row r="610" spans="1:7">
+      <c r="A610" s="4">
         <v>44440</v>
       </c>
       <c r="B610" s="4">
@@ -11174,8 +11165,8 @@
       </c>
       <c r="G610" s="3"/>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A611" s="9">
+    <row r="611" spans="1:7">
+      <c r="A611" s="4">
         <v>44470</v>
       </c>
       <c r="B611" s="4">
@@ -11192,8 +11183,8 @@
       </c>
       <c r="G611" s="3"/>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A612" s="9">
+    <row r="612" spans="1:7">
+      <c r="A612" s="4">
         <v>44501</v>
       </c>
       <c r="B612" s="4">
@@ -11210,8 +11201,8 @@
       </c>
       <c r="G612" s="3"/>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A613" s="9">
+    <row r="613" spans="1:7">
+      <c r="A613" s="4">
         <v>44531</v>
       </c>
       <c r="B613" s="4">
@@ -11228,8 +11219,8 @@
       </c>
       <c r="G613" s="3"/>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A614" s="9">
+    <row r="614" spans="1:7">
+      <c r="A614" s="4">
         <v>44562</v>
       </c>
       <c r="B614" s="4">
@@ -11246,8 +11237,8 @@
       </c>
       <c r="G614" s="3"/>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A615" s="9">
+    <row r="615" spans="1:7">
+      <c r="A615" s="4">
         <v>44593</v>
       </c>
       <c r="B615" s="4">
@@ -11264,8 +11255,8 @@
       </c>
       <c r="G615" s="3"/>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A616" s="9">
+    <row r="616" spans="1:7">
+      <c r="A616" s="4">
         <v>44621</v>
       </c>
       <c r="B616" s="4">
@@ -11282,8 +11273,8 @@
       </c>
       <c r="G616" s="3"/>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A617" s="9">
+    <row r="617" spans="1:7">
+      <c r="A617" s="4">
         <v>44652</v>
       </c>
       <c r="B617" s="4">
@@ -11300,8 +11291,8 @@
       </c>
       <c r="G617" s="3"/>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A618" s="9">
+    <row r="618" spans="1:7">
+      <c r="A618" s="4">
         <v>44682</v>
       </c>
       <c r="B618" s="4">
@@ -11318,8 +11309,8 @@
       </c>
       <c r="G618" s="3"/>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A619" s="9">
+    <row r="619" spans="1:7">
+      <c r="A619" s="4">
         <v>44713</v>
       </c>
       <c r="B619" s="4">
@@ -11336,8 +11327,8 @@
       </c>
       <c r="G619" s="3"/>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A620" s="9">
+    <row r="620" spans="1:7">
+      <c r="A620" s="4">
         <v>44743</v>
       </c>
       <c r="B620" s="4">
@@ -11354,8 +11345,8 @@
       </c>
       <c r="G620" s="3"/>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A621" s="9">
+    <row r="621" spans="1:7">
+      <c r="A621" s="4">
         <v>44774</v>
       </c>
       <c r="B621" s="4">
@@ -11372,8 +11363,8 @@
       </c>
       <c r="G621" s="3"/>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A622" s="9">
+    <row r="622" spans="1:7">
+      <c r="A622" s="4">
         <v>44805</v>
       </c>
       <c r="B622" s="4">
@@ -11390,8 +11381,8 @@
       </c>
       <c r="G622" s="3"/>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A623" s="9">
+    <row r="623" spans="1:7">
+      <c r="A623" s="4">
         <v>44835</v>
       </c>
       <c r="B623" s="4">
@@ -11408,8 +11399,8 @@
       </c>
       <c r="G623" s="3"/>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A624" s="9">
+    <row r="624" spans="1:7">
+      <c r="A624" s="4">
         <v>44866</v>
       </c>
       <c r="B624" s="4">
@@ -11426,8 +11417,8 @@
       </c>
       <c r="G624" s="3"/>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A625" s="9">
+    <row r="625" spans="1:7">
+      <c r="A625" s="4">
         <v>44896</v>
       </c>
       <c r="B625" s="4">
@@ -11444,8 +11435,8 @@
       </c>
       <c r="G625" s="3"/>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A626" s="9">
+    <row r="626" spans="1:7">
+      <c r="A626" s="4">
         <v>44927</v>
       </c>
       <c r="B626" s="4">
@@ -11462,8 +11453,8 @@
       </c>
       <c r="G626" s="3"/>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A627" s="9">
+    <row r="627" spans="1:7">
+      <c r="A627" s="4">
         <v>44958</v>
       </c>
       <c r="B627" s="4">
@@ -11480,8 +11471,8 @@
       </c>
       <c r="G627" s="3"/>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A628" s="9">
+    <row r="628" spans="1:7">
+      <c r="A628" s="4">
         <v>44986</v>
       </c>
       <c r="B628" s="4">
@@ -11501,8 +11492,8 @@
       </c>
       <c r="G628" s="3"/>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A629" s="9">
+    <row r="629" spans="1:7">
+      <c r="A629" s="4">
         <v>45017</v>
       </c>
       <c r="B629" s="4">
@@ -11522,8 +11513,8 @@
       </c>
       <c r="G629" s="3"/>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A630" s="9">
+    <row r="630" spans="1:7">
+      <c r="A630" s="4">
         <v>45047</v>
       </c>
       <c r="B630" s="4">
@@ -11543,8 +11534,8 @@
       </c>
       <c r="G630" s="3"/>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A631" s="9">
+    <row r="631" spans="1:7">
+      <c r="A631" s="4">
         <v>45078</v>
       </c>
       <c r="B631" s="4">
@@ -11564,8 +11555,8 @@
       </c>
       <c r="G631" s="3"/>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A632" s="9">
+    <row r="632" spans="1:7">
+      <c r="A632" s="4">
         <v>45108</v>
       </c>
       <c r="B632" s="4">
@@ -11585,8 +11576,8 @@
       </c>
       <c r="G632" s="3"/>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A633" s="9">
+    <row r="633" spans="1:7">
+      <c r="A633" s="4">
         <v>45139</v>
       </c>
       <c r="B633" s="4">
@@ -11603,8 +11594,8 @@
       </c>
       <c r="G633" s="3"/>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A634" s="9">
+    <row r="634" spans="1:7">
+      <c r="A634" s="4">
         <v>45170</v>
       </c>
       <c r="B634" s="4">
@@ -11621,8 +11612,8 @@
       </c>
       <c r="G634" s="3"/>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A635" s="9">
+    <row r="635" spans="1:7">
+      <c r="A635" s="4">
         <v>45200</v>
       </c>
       <c r="B635" s="4">
@@ -11642,8 +11633,8 @@
       </c>
       <c r="G635" s="3"/>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A636" s="9">
+    <row r="636" spans="1:7">
+      <c r="A636" s="4">
         <v>45231</v>
       </c>
       <c r="B636" s="4">
@@ -11660,8 +11651,8 @@
       </c>
       <c r="G636" s="3"/>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A637" s="9">
+    <row r="637" spans="1:7">
+      <c r="A637" s="4">
         <v>45261</v>
       </c>
       <c r="B637" s="4">
@@ -11678,8 +11669,8 @@
       </c>
       <c r="G637" s="3"/>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A638" s="9">
+    <row r="638" spans="1:7">
+      <c r="A638" s="4">
         <v>45292</v>
       </c>
       <c r="B638" s="4">
@@ -11696,8 +11687,8 @@
       </c>
       <c r="G638" s="3"/>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A639" s="9">
+    <row r="639" spans="1:7">
+      <c r="A639" s="4">
         <v>45323</v>
       </c>
       <c r="B639" s="4">
@@ -11714,8 +11705,8 @@
       </c>
       <c r="G639" s="3"/>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A640" s="9">
+    <row r="640" spans="1:7">
+      <c r="A640" s="4">
         <v>45352</v>
       </c>
       <c r="B640" s="4">
@@ -11735,8 +11726,8 @@
       </c>
       <c r="G640" s="3"/>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A641" s="9">
+    <row r="641" spans="1:7">
+      <c r="A641" s="4">
         <v>45383</v>
       </c>
       <c r="B641" s="4">
@@ -11753,8 +11744,8 @@
       </c>
       <c r="G641" s="3"/>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A642" s="9">
+    <row r="642" spans="1:7">
+      <c r="A642" s="4">
         <v>45413</v>
       </c>
       <c r="B642" s="4">
@@ -11771,8 +11762,8 @@
       </c>
       <c r="G642" s="3"/>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A643" s="9">
+    <row r="643" spans="1:7">
+      <c r="A643" s="4">
         <v>45444</v>
       </c>
       <c r="B643" s="4">
@@ -11789,8 +11780,8 @@
       </c>
       <c r="G643" s="3"/>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A644" s="9">
+    <row r="644" spans="1:7">
+      <c r="A644" s="4">
         <v>45474</v>
       </c>
       <c r="B644" s="4">
@@ -11810,8 +11801,8 @@
       </c>
       <c r="G644" s="3"/>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A645" s="9">
+    <row r="645" spans="1:7">
+      <c r="A645" s="4">
         <v>45505</v>
       </c>
       <c r="B645" s="4">
@@ -11828,8 +11819,8 @@
       </c>
       <c r="G645" s="3"/>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A646" s="9">
+    <row r="646" spans="1:7">
+      <c r="A646" s="4">
         <v>45536</v>
       </c>
       <c r="B646" s="4">
@@ -11846,8 +11837,8 @@
       </c>
       <c r="G646" s="3"/>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A647" s="9">
+    <row r="647" spans="1:7">
+      <c r="A647" s="4">
         <v>45566</v>
       </c>
       <c r="B647" s="4">
@@ -11864,8 +11855,8 @@
       </c>
       <c r="G647" s="3"/>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A648" s="9">
+    <row r="648" spans="1:7">
+      <c r="A648" s="4">
         <v>45597</v>
       </c>
       <c r="B648" s="4">
@@ -11882,8 +11873,8 @@
       </c>
       <c r="G648" s="3"/>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A649" s="9">
+    <row r="649" spans="1:7">
+      <c r="A649" s="4">
         <v>45627</v>
       </c>
       <c r="B649" s="4">
@@ -11900,8 +11891,8 @@
       </c>
       <c r="G649" s="3"/>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A650" s="9">
+    <row r="650" spans="1:7">
+      <c r="A650" s="4">
         <v>45658</v>
       </c>
       <c r="B650" s="4">
@@ -11918,8 +11909,8 @@
       </c>
       <c r="G650" s="3"/>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A651" s="9">
+    <row r="651" spans="1:7">
+      <c r="A651" s="4">
         <v>45689</v>
       </c>
       <c r="B651" s="4">
@@ -11936,8 +11927,8 @@
       </c>
       <c r="G651" s="3"/>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A652" s="9">
+    <row r="652" spans="1:7">
+      <c r="A652" s="4">
         <v>45717</v>
       </c>
       <c r="B652" s="4">
@@ -11954,8 +11945,8 @@
       </c>
       <c r="G652" s="3"/>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A653" s="9">
+    <row r="653" spans="1:7">
+      <c r="A653" s="4">
         <v>45748</v>
       </c>
       <c r="B653" s="4">
@@ -11972,8 +11963,8 @@
       </c>
       <c r="G653" s="3"/>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A654" s="9">
+    <row r="654" spans="1:7">
+      <c r="A654" s="4">
         <v>45778</v>
       </c>
       <c r="B654" s="4">
@@ -11993,8 +11984,8 @@
       </c>
       <c r="G654" s="3"/>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A655" s="9">
+    <row r="655" spans="1:7">
+      <c r="A655" s="4">
         <v>45809</v>
       </c>
       <c r="B655" s="4">
@@ -12011,8 +12002,8 @@
       </c>
       <c r="G655" s="3"/>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A656" s="9">
+    <row r="656" spans="1:7">
+      <c r="A656" s="4">
         <v>45839</v>
       </c>
       <c r="B656" s="4">
@@ -12029,8 +12020,8 @@
       </c>
       <c r="G656" s="3"/>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A657" s="9">
+    <row r="657" spans="1:7">
+      <c r="A657" s="4">
         <v>45870</v>
       </c>
       <c r="B657" s="4">
@@ -12047,8 +12038,8 @@
       </c>
       <c r="G657" s="3"/>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A658" s="9">
+    <row r="658" spans="1:7">
+      <c r="A658" s="4">
         <v>45901</v>
       </c>
       <c r="B658" s="4">
@@ -12065,8 +12056,8 @@
       </c>
       <c r="G658" s="3"/>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A659" s="9">
+    <row r="659" spans="1:7">
+      <c r="A659" s="4">
         <v>45931</v>
       </c>
       <c r="B659" s="4">
@@ -12083,8 +12074,8 @@
       </c>
       <c r="G659" s="3"/>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A660" s="9">
+    <row r="660" spans="1:7">
+      <c r="A660" s="4">
         <v>45962</v>
       </c>
       <c r="B660" s="4">
@@ -12102,7 +12093,7 @@
       <c r="G660" s="3"/>
     </row>
   </sheetData>
-  <sortState ref="B2:F662">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F662">
     <sortCondition ref="B2:B662"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12113,12 +12104,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7043F4AB-5389-4625-9F9F-4D4B26DB20C4}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
@@ -12126,7 +12117,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3">
       <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
